--- a/調査内容/アウトプット.xlsx
+++ b/調査内容/アウトプット.xlsx
@@ -5,15 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c9734a6374d7513b/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\aaa\elkstack\調査内容\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="8_{0792F530-A896-4189-8C10-D2CE96C722F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F1AFF03-81AA-4095-8ACB-6B9962FC5E10}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{759E1AAA-74F4-4A18-A7D8-E7969CB8467A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FE37317B-BE23-49EA-9156-A5F997289FA1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{FE37317B-BE23-49EA-9156-A5F997289FA1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="26">
   <si>
     <t>徐々に上昇、減少する値が一定値を超えたら</t>
     <rPh sb="0" eb="2">
@@ -310,6 +312,59 @@
     </rPh>
     <rPh sb="10" eb="11">
       <t>コ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>固定閾値</t>
+    <rPh sb="0" eb="2">
+      <t>コテイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シキイチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>複合</t>
+    <rPh sb="0" eb="2">
+      <t>フクゴウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>pmup-01</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>motor-01</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ルール</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>振動</t>
+    <rPh sb="0" eb="2">
+      <t>シンドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>異常検知</t>
+    <rPh sb="0" eb="2">
+      <t>イジョウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ケンチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>異常検知_振動_固定閾値</t>
+    <rPh sb="5" eb="7">
+      <t>シンドウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -357,12 +412,18 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -790,4 +851,101 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7006C1DB-98F9-48B9-8DF9-15263F9D11B6}">
+  <dimension ref="B3:O8"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="2" max="2" width="24.25" customWidth="1"/>
+    <col min="3" max="3" width="42" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="D3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+      <c r="M3" s="3"/>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+    </row>
+    <row r="4" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="D4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+    </row>
+    <row r="5" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="D5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+    </row>
+    <row r="6" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="D6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="C8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="3"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="E5:G5"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="D4:G4"/>
+    <mergeCell ref="D3:O3"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A27E796B-F459-4C11-A282-26B4A543F32F}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/調査内容/アウトプット.xlsx
+++ b/調査内容/アウトプット.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\aaa\elkstack\調査内容\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{759E1AAA-74F4-4A18-A7D8-E7969CB8467A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61E89901-DC71-4E62-8714-E748C98962EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{FE37317B-BE23-49EA-9156-A5F997289FA1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{FE37317B-BE23-49EA-9156-A5F997289FA1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId2"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
+    <sheet name="GmailでSMTP送信する設定" sheetId="4" r:id="rId3"/>
+    <sheet name="GmailでSMTP送信する設定 (2)" sheetId="6" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="86">
   <si>
     <t>徐々に上昇、減少する値が一定値を超えたら</t>
     <rPh sb="0" eb="2">
@@ -368,12 +369,399 @@
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>ダッシューボード</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ジョブ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>vibration-anomaly-detection</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>vibration-pmup-01-anomaly-detection</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>vibration-motor-01-anomaly-detection</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データビュー（検索）</t>
+    <rPh sb="7" eb="9">
+      <t>ケンサク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>sensor-data</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>sensor-data-pmup-01</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>sensor-data-motor-01</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>異常検知_振動_機械学習_徐々に変化</t>
+    <rPh sb="16" eb="18">
+      <t>ヘンカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>異常検知_振動_機械学習_急激に変化</t>
+    <rPh sb="13" eb="15">
+      <t>キュウゲキ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ヘンカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>異常検知_振動_機械学習_徐々に変化_pmup-01のみ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>異常検知_振動_機械学習_徐々に変化_motor-01のみ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>異常検知_振動_機械学習_急激に変化_pmup-01のみ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>異常検知_振動_機械学習_急激に変化_motor-01のみ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>GmailでSMTP送信する設定</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1.Gmail側の準備（アプリパスワードの生成）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1-1. 下記のURLに接続する。</t>
+    <rPh sb="5" eb="7">
+      <t>カキ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>セツゾク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（URL）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>https://myaccount.google.com/apppasswords</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（画面）</t>
+    <rPh sb="1" eb="3">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1-2. アプリ名の欄に「Kibana」と入力し、画面右下の「作成」ボタンを押下する。</t>
+    <rPh sb="8" eb="9">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ミギシタ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1-3. 青枠に表示される16文字のパスワードをメモしておき、画面右下の「完了」ボタンを押下する。</t>
+    <rPh sb="5" eb="7">
+      <t>アオワク</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>ミギシタ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2.SMTP認証ファイルを作成</t>
+    <rPh sb="6" eb="8">
+      <t>ニンショウ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2-1. PowerShellでsmtp_auth.yamlを作成する。</t>
+    <rPh sb="31" eb="33">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>@"</t>
+  </si>
+  <si>
+    <t>user: "your-email@gmail.com"</t>
+  </si>
+  <si>
+    <t>password: "xxxx xxxx xxxx xxxx"</t>
+  </si>
+  <si>
+    <t>← 手順「1-3.」でメモしたパスワードを入力</t>
+    <rPh sb="2" eb="4">
+      <t>テジュン</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>@ | Out-File -FilePath $env:USERPROFILE\smtp_auth.yaml" -Encoding utf8</t>
+  </si>
+  <si>
+    <t>2-2. elastalert コンテナにコピーする。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>podman cp $env:USERPROFILE\smtp_auth.yaml elastalert:/opt/elastalert/smtp_auth.yaml</t>
+  </si>
+  <si>
+    <t>2-3. コンテナ内にコピーできたか確認する。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>podman exec -it elastalert cat /opt/elastalert/smtp_auth.yaml</t>
+  </si>
+  <si>
+    <t>手順「2-1.」で入力した情報が表示されれば作成完了。</t>
+    <rPh sb="0" eb="2">
+      <t>テジュン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>カンリョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Analytics - Discover</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>機械学習 - 異常検知 - ジョブ</t>
+    <rPh sb="0" eb="2">
+      <t>キカイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ガクシュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>固定閾値</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>機械学習 - 異常検知 - 異常エクスプローラー</t>
+    <rPh sb="0" eb="2">
+      <t>キカイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ガクシュウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>イジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>機械学習 - 異常検知 - シングルメトリックビューワー</t>
+    <rPh sb="0" eb="2">
+      <t>キカイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ガクシュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Security - ルール</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Security - アラート</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Analytics - Dashboards</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>条件に一致したログの一覧表示。検索結果の保存。</t>
+    <rPh sb="15" eb="17">
+      <t>ケンサク</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ホゾン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>異常検知モデルの学習・管理。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>単一指標の時系列グラフと異常箇所のハイライト表示。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>発生アラートの一覧・ステータス管理・詳細レポート。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>グラフ・表・数値を組み合わせたダッシュボード画面。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>異常スコア付きのタイムライングラフ。異常イベント一覧表示。</t>
+    <rPh sb="26" eb="28">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>機械学習</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>徐々に変化</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>急激に変化</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>機能</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>機能を使用してできること</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>分析方法</t>
+    <rPh sb="0" eb="2">
+      <t>ブンセキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ホウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>〇</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>検知ルールの一覧表示・作成。ルールの有効化／無効化。</t>
+    <rPh sb="11" eb="13">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>.分析方法毎による</t>
+    <rPh sb="1" eb="3">
+      <t>ブンセキ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ホウホウ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ゴト</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>.設定手順</t>
+    <rPh sb="1" eb="3">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>テジュン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -389,16 +777,61 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.749992370372631"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -406,13 +839,189 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border diagonalDown="1">
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal style="thin">
+        <color indexed="64"/>
+      </diagonal>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -422,11 +1031,128 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="4">
+    <cellStyle name="ハイパーリンク" xfId="3" builtinId="8"/>
+    <cellStyle name="見出し 2" xfId="1" builtinId="17"/>
+    <cellStyle name="見出し 3" xfId="2" builtinId="18"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -440,6 +1166,376 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>177258</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27D46D6A-CF8B-4D05-90AB-11D2E6817ABB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="952500" y="1752600"/>
+          <a:ext cx="7858125" cy="3577683"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>185467</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>177258</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="3" name="グループ化 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{752394F9-050B-4D63-AFD5-0FBFAC5413A4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="714375" y="5753100"/>
+          <a:ext cx="7805467" cy="3577683"/>
+          <a:chOff x="714375" y="5953125"/>
+          <a:chExt cx="7805467" cy="3577683"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="4" name="図 3">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5BB6349E-BB39-2B7E-DE17-75E64CC8B714}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+            <a:extLst>
+              <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+              </a:ext>
+            </a:extLst>
+          </a:blip>
+          <a:srcRect/>
+          <a:stretch/>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="714375" y="5953125"/>
+            <a:ext cx="7805467" cy="3577683"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="5" name="正方形/長方形 4">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{842BC55A-FF68-C290-54F2-4A554ED79B0D}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="4972050" y="8296276"/>
+            <a:ext cx="504825" cy="342900"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>124573</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>48246</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="6" name="グループ化 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A90DDB43-E7EB-4042-BAF2-5687F0ADB48B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="714375" y="9753600"/>
+          <a:ext cx="5363323" cy="4448796"/>
+          <a:chOff x="714375" y="9953625"/>
+          <a:chExt cx="5363323" cy="4448796"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="7" name="グループ化 6">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FA148B37-D345-6BA0-5252-8DB441394CFE}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="714375" y="9953625"/>
+            <a:ext cx="5363323" cy="4448796"/>
+            <a:chOff x="714375" y="9953625"/>
+            <a:chExt cx="5363323" cy="4448796"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="9" name="図 8">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DDD24BFB-1D18-D8C5-B306-D6246583F17A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="714375" y="9953625"/>
+              <a:ext cx="5363323" cy="4448796"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:ln>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="10" name="正方形/長方形 9">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE18D223-69CC-9948-2974-D0ED9E5C8B29}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="1943100" y="11144250"/>
+              <a:ext cx="3124200" cy="600076"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="2">
+              <a:schemeClr val="accent1">
+                <a:shade val="15000"/>
+              </a:schemeClr>
+            </a:lnRef>
+            <a:fillRef idx="1">
+              <a:schemeClr val="accent1"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:schemeClr val="accent1"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="lt1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </xdr:grpSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="8" name="正方形/長方形 7">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{116ADD06-5909-E4E5-6AEB-13BE75EDAE33}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="5076825" y="13649324"/>
+            <a:ext cx="885825" cy="638175"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -855,29 +1951,32 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7006C1DB-98F9-48B9-8DF9-15263F9D11B6}">
-  <dimension ref="B3:O8"/>
+  <dimension ref="B3:O27"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="24.25" customWidth="1"/>
     <col min="3" max="3" width="42" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="23.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="35.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="49.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="49" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:15" x14ac:dyDescent="0.4">
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.4">
       <c r="D4" s="3" t="s">
@@ -888,7 +1987,7 @@
       <c r="G4" s="3"/>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.4">
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="4" t="s">
         <v>18</v>
       </c>
       <c r="E5" s="3" t="s">
@@ -898,42 +1997,218 @@
       <c r="G5" s="3"/>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.4">
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="4" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.4">
       <c r="B7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="6"/>
+      <c r="E8" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B9" t="s">
         <v>22</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C9" t="s">
         <v>0</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.4">
-      <c r="C8" t="s">
+      <c r="E9" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="C10" t="s">
         <v>1</v>
       </c>
-      <c r="D8" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="B11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="C12" t="s">
+        <v>1</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="D13" s="5"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
+    </row>
+    <row r="14" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+    </row>
+    <row r="15" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+    </row>
+    <row r="16" spans="2:15" x14ac:dyDescent="0.4">
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
+    </row>
+    <row r="17" spans="4:7" x14ac:dyDescent="0.4">
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
+    </row>
+    <row r="18" spans="4:7" x14ac:dyDescent="0.4">
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+    </row>
+    <row r="19" spans="4:7" x14ac:dyDescent="0.4">
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.4">
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+    </row>
+    <row r="21" spans="4:7" x14ac:dyDescent="0.4">
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+    </row>
+    <row r="22" spans="4:7" x14ac:dyDescent="0.4">
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+    </row>
+    <row r="23" spans="4:7" x14ac:dyDescent="0.4">
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+    </row>
+    <row r="24" spans="4:7" x14ac:dyDescent="0.4">
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+    </row>
+    <row r="25" spans="4:7" x14ac:dyDescent="0.4">
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+    </row>
+    <row r="26" spans="4:7" x14ac:dyDescent="0.4">
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+    </row>
+    <row r="27" spans="4:7" x14ac:dyDescent="0.4">
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="E5:G5"/>
-    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="D9:D10"/>
     <mergeCell ref="D4:G4"/>
     <mergeCell ref="D3:O3"/>
+    <mergeCell ref="D11:D12"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -941,11 +2216,992 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A27E796B-F459-4C11-A282-26B4A543F32F}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10383A97-FD6D-4BA6-BD6A-9660CCB92064}">
+  <dimension ref="A1:AF86"/>
+  <sheetFormatPr defaultColWidth="3.125" defaultRowHeight="15.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="16384" width="3.125" style="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="21" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="16.5" thickTop="1" x14ac:dyDescent="0.4"/>
+    <row r="3" spans="1:5" ht="18.75" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B3" s="9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="C4" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="D5" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="E6" s="10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="D8" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="28" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C28" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="48" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C48" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" ht="18.75" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B73" s="9" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.4">
+      <c r="C74" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.4">
+      <c r="D75" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E75" s="12"/>
+      <c r="F75" s="12"/>
+      <c r="G75" s="12"/>
+      <c r="H75" s="12"/>
+      <c r="I75" s="12"/>
+      <c r="J75" s="12"/>
+      <c r="K75" s="12"/>
+      <c r="L75" s="12"/>
+      <c r="M75" s="12"/>
+      <c r="N75" s="12"/>
+      <c r="O75" s="12"/>
+      <c r="P75" s="12"/>
+      <c r="Q75" s="12"/>
+      <c r="R75" s="12"/>
+      <c r="S75" s="12"/>
+      <c r="T75" s="12"/>
+      <c r="U75" s="12"/>
+      <c r="V75" s="12"/>
+      <c r="W75" s="12"/>
+      <c r="X75" s="12"/>
+      <c r="Y75" s="12"/>
+      <c r="Z75" s="12"/>
+      <c r="AA75" s="12"/>
+      <c r="AB75" s="12"/>
+      <c r="AC75" s="13"/>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.4">
+      <c r="D76" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC76" s="15"/>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.4">
+      <c r="D77" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="AC77" s="15"/>
+      <c r="AD77" s="8" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="78" spans="2:30" x14ac:dyDescent="0.4">
+      <c r="D78" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="E78" s="17"/>
+      <c r="F78" s="17"/>
+      <c r="G78" s="17"/>
+      <c r="H78" s="17"/>
+      <c r="I78" s="17"/>
+      <c r="J78" s="17"/>
+      <c r="K78" s="17"/>
+      <c r="L78" s="17"/>
+      <c r="M78" s="17"/>
+      <c r="N78" s="17"/>
+      <c r="O78" s="17"/>
+      <c r="P78" s="17"/>
+      <c r="Q78" s="17"/>
+      <c r="R78" s="17"/>
+      <c r="S78" s="17"/>
+      <c r="T78" s="17"/>
+      <c r="U78" s="17"/>
+      <c r="V78" s="17"/>
+      <c r="W78" s="17"/>
+      <c r="X78" s="17"/>
+      <c r="Y78" s="17"/>
+      <c r="Z78" s="17"/>
+      <c r="AA78" s="17"/>
+      <c r="AB78" s="17"/>
+      <c r="AC78" s="18"/>
+    </row>
+    <row r="80" spans="2:30" x14ac:dyDescent="0.4">
+      <c r="C80" s="8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="81" spans="3:32" x14ac:dyDescent="0.4">
+      <c r="D81" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="E81" s="20"/>
+      <c r="F81" s="20"/>
+      <c r="G81" s="20"/>
+      <c r="H81" s="20"/>
+      <c r="I81" s="20"/>
+      <c r="J81" s="20"/>
+      <c r="K81" s="20"/>
+      <c r="L81" s="20"/>
+      <c r="M81" s="20"/>
+      <c r="N81" s="20"/>
+      <c r="O81" s="20"/>
+      <c r="P81" s="20"/>
+      <c r="Q81" s="20"/>
+      <c r="R81" s="20"/>
+      <c r="S81" s="20"/>
+      <c r="T81" s="20"/>
+      <c r="U81" s="20"/>
+      <c r="V81" s="20"/>
+      <c r="W81" s="20"/>
+      <c r="X81" s="20"/>
+      <c r="Y81" s="20"/>
+      <c r="Z81" s="20"/>
+      <c r="AA81" s="20"/>
+      <c r="AB81" s="20"/>
+      <c r="AC81" s="20"/>
+      <c r="AD81" s="20"/>
+      <c r="AE81" s="20"/>
+      <c r="AF81" s="21"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.4">
+      <c r="C83" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.4">
+      <c r="D84" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="E84" s="20"/>
+      <c r="F84" s="20"/>
+      <c r="G84" s="20"/>
+      <c r="H84" s="20"/>
+      <c r="I84" s="20"/>
+      <c r="J84" s="20"/>
+      <c r="K84" s="20"/>
+      <c r="L84" s="20"/>
+      <c r="M84" s="20"/>
+      <c r="N84" s="20"/>
+      <c r="O84" s="20"/>
+      <c r="P84" s="20"/>
+      <c r="Q84" s="20"/>
+      <c r="R84" s="20"/>
+      <c r="S84" s="20"/>
+      <c r="T84" s="20"/>
+      <c r="U84" s="20"/>
+      <c r="V84" s="20"/>
+      <c r="W84" s="20"/>
+      <c r="X84" s="20"/>
+      <c r="Y84" s="20"/>
+      <c r="Z84" s="20"/>
+      <c r="AA84" s="20"/>
+      <c r="AB84" s="20"/>
+      <c r="AC84" s="20"/>
+      <c r="AD84" s="20"/>
+      <c r="AE84" s="20"/>
+      <c r="AF84" s="21"/>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.4">
+      <c r="D86" s="8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="E6" r:id="rId1" xr:uid="{9EB54B52-0500-478E-9711-8C1BBA1121BE}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EE2507A-85E3-4A77-8023-F37EE69F3B29}">
+  <dimension ref="A1:BC87"/>
+  <sheetFormatPr defaultColWidth="3.125" defaultRowHeight="15.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="16384" width="3.125" style="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:55" ht="21" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:55" ht="16.5" thickTop="1" x14ac:dyDescent="0.4"/>
+    <row r="3" spans="1:55" ht="18.75" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B3" s="9" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:55" x14ac:dyDescent="0.4">
+      <c r="C4" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:55" x14ac:dyDescent="0.4">
+      <c r="D5" s="8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:55" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="E6" s="10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:55" ht="18.75" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B10" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="BC10" s="22"/>
+    </row>
+    <row r="15" spans="1:55" ht="18.75" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B15" s="9" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17" spans="3:43" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="18" spans="3:43" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="19" spans="3:43" x14ac:dyDescent="0.4">
+      <c r="C19" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="D19" s="28"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="28"/>
+      <c r="H19" s="28"/>
+      <c r="I19" s="28"/>
+      <c r="J19" s="28"/>
+      <c r="K19" s="28"/>
+      <c r="L19" s="28"/>
+      <c r="M19" s="28"/>
+      <c r="N19" s="28"/>
+      <c r="O19" s="28"/>
+      <c r="P19" s="29"/>
+      <c r="Q19" s="27" t="s">
+        <v>79</v>
+      </c>
+      <c r="R19" s="28"/>
+      <c r="S19" s="28"/>
+      <c r="T19" s="28"/>
+      <c r="U19" s="28"/>
+      <c r="V19" s="28"/>
+      <c r="W19" s="28"/>
+      <c r="X19" s="28"/>
+      <c r="Y19" s="28"/>
+      <c r="Z19" s="28"/>
+      <c r="AA19" s="28"/>
+      <c r="AB19" s="28"/>
+      <c r="AC19" s="28"/>
+      <c r="AD19" s="28"/>
+      <c r="AE19" s="29"/>
+      <c r="AF19" s="30" t="s">
+        <v>80</v>
+      </c>
+      <c r="AG19" s="31"/>
+      <c r="AH19" s="31"/>
+      <c r="AI19" s="31"/>
+      <c r="AJ19" s="31"/>
+      <c r="AK19" s="31"/>
+      <c r="AL19" s="31"/>
+      <c r="AM19" s="31"/>
+      <c r="AN19" s="31"/>
+      <c r="AO19" s="31"/>
+      <c r="AP19" s="31"/>
+      <c r="AQ19" s="32"/>
+    </row>
+    <row r="20" spans="3:43" x14ac:dyDescent="0.4">
+      <c r="C20" s="33"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="34"/>
+      <c r="G20" s="34"/>
+      <c r="H20" s="34"/>
+      <c r="I20" s="34"/>
+      <c r="J20" s="34"/>
+      <c r="K20" s="34"/>
+      <c r="L20" s="34"/>
+      <c r="M20" s="34"/>
+      <c r="N20" s="34"/>
+      <c r="O20" s="34"/>
+      <c r="P20" s="35"/>
+      <c r="Q20" s="33"/>
+      <c r="R20" s="34"/>
+      <c r="S20" s="34"/>
+      <c r="T20" s="34"/>
+      <c r="U20" s="34"/>
+      <c r="V20" s="34"/>
+      <c r="W20" s="34"/>
+      <c r="X20" s="34"/>
+      <c r="Y20" s="34"/>
+      <c r="Z20" s="34"/>
+      <c r="AA20" s="34"/>
+      <c r="AB20" s="34"/>
+      <c r="AC20" s="34"/>
+      <c r="AD20" s="34"/>
+      <c r="AE20" s="35"/>
+      <c r="AF20" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="AG20" s="28"/>
+      <c r="AH20" s="28"/>
+      <c r="AI20" s="29"/>
+      <c r="AJ20" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="AK20" s="28"/>
+      <c r="AL20" s="28"/>
+      <c r="AM20" s="29"/>
+      <c r="AN20" s="27" t="s">
+        <v>75</v>
+      </c>
+      <c r="AO20" s="28"/>
+      <c r="AP20" s="28"/>
+      <c r="AQ20" s="29"/>
+    </row>
+    <row r="21" spans="3:43" x14ac:dyDescent="0.4">
+      <c r="C21" s="36"/>
+      <c r="D21" s="37"/>
+      <c r="E21" s="37"/>
+      <c r="F21" s="37"/>
+      <c r="G21" s="37"/>
+      <c r="H21" s="37"/>
+      <c r="I21" s="37"/>
+      <c r="J21" s="37"/>
+      <c r="K21" s="37"/>
+      <c r="L21" s="37"/>
+      <c r="M21" s="37"/>
+      <c r="N21" s="37"/>
+      <c r="O21" s="37"/>
+      <c r="P21" s="38"/>
+      <c r="Q21" s="36"/>
+      <c r="R21" s="37"/>
+      <c r="S21" s="37"/>
+      <c r="T21" s="37"/>
+      <c r="U21" s="37"/>
+      <c r="V21" s="37"/>
+      <c r="W21" s="37"/>
+      <c r="X21" s="37"/>
+      <c r="Y21" s="37"/>
+      <c r="Z21" s="37"/>
+      <c r="AA21" s="37"/>
+      <c r="AB21" s="37"/>
+      <c r="AC21" s="37"/>
+      <c r="AD21" s="37"/>
+      <c r="AE21" s="38"/>
+      <c r="AF21" s="39"/>
+      <c r="AG21" s="40"/>
+      <c r="AH21" s="40"/>
+      <c r="AI21" s="41"/>
+      <c r="AJ21" s="39" t="s">
+        <v>76</v>
+      </c>
+      <c r="AK21" s="40"/>
+      <c r="AL21" s="40"/>
+      <c r="AM21" s="38"/>
+      <c r="AN21" s="39" t="s">
+        <v>77</v>
+      </c>
+      <c r="AO21" s="40"/>
+      <c r="AP21" s="40"/>
+      <c r="AQ21" s="41"/>
+    </row>
+    <row r="22" spans="3:43" x14ac:dyDescent="0.4">
+      <c r="C22" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="20"/>
+      <c r="I22" s="20"/>
+      <c r="J22" s="20"/>
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+      <c r="M22" s="20"/>
+      <c r="N22" s="20"/>
+      <c r="O22" s="20"/>
+      <c r="P22" s="21"/>
+      <c r="Q22" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="R22" s="20"/>
+      <c r="S22" s="20"/>
+      <c r="T22" s="20"/>
+      <c r="U22" s="20"/>
+      <c r="V22" s="20"/>
+      <c r="W22" s="20"/>
+      <c r="X22" s="20"/>
+      <c r="Y22" s="20"/>
+      <c r="Z22" s="20"/>
+      <c r="AA22" s="20"/>
+      <c r="AB22" s="20"/>
+      <c r="AC22" s="20"/>
+      <c r="AD22" s="20"/>
+      <c r="AE22" s="21"/>
+      <c r="AF22" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="AG22" s="24"/>
+      <c r="AH22" s="24"/>
+      <c r="AI22" s="26"/>
+      <c r="AJ22" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="AK22" s="25"/>
+      <c r="AL22" s="25"/>
+      <c r="AM22" s="25"/>
+      <c r="AN22" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="AO22" s="25"/>
+      <c r="AP22" s="25"/>
+      <c r="AQ22" s="25"/>
+    </row>
+    <row r="23" spans="3:43" x14ac:dyDescent="0.4">
+      <c r="C23" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
+      <c r="I23" s="20"/>
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+      <c r="M23" s="20"/>
+      <c r="N23" s="20"/>
+      <c r="O23" s="20"/>
+      <c r="P23" s="21"/>
+      <c r="Q23" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="R23" s="20"/>
+      <c r="S23" s="20"/>
+      <c r="T23" s="20"/>
+      <c r="U23" s="20"/>
+      <c r="V23" s="20"/>
+      <c r="W23" s="20"/>
+      <c r="X23" s="20"/>
+      <c r="Y23" s="20"/>
+      <c r="Z23" s="20"/>
+      <c r="AA23" s="20"/>
+      <c r="AB23" s="20"/>
+      <c r="AC23" s="20"/>
+      <c r="AD23" s="20"/>
+      <c r="AE23" s="21"/>
+      <c r="AF23" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="AG23" s="24"/>
+      <c r="AH23" s="24"/>
+      <c r="AI23" s="26"/>
+      <c r="AJ23" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="AK23" s="25"/>
+      <c r="AL23" s="25"/>
+      <c r="AM23" s="25"/>
+      <c r="AN23" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="AO23" s="25"/>
+      <c r="AP23" s="25"/>
+      <c r="AQ23" s="25"/>
+    </row>
+    <row r="24" spans="3:43" x14ac:dyDescent="0.4">
+      <c r="C24" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="20"/>
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+      <c r="M24" s="20"/>
+      <c r="N24" s="20"/>
+      <c r="O24" s="20"/>
+      <c r="P24" s="21"/>
+      <c r="Q24" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="R24" s="20"/>
+      <c r="S24" s="20"/>
+      <c r="T24" s="20"/>
+      <c r="U24" s="20"/>
+      <c r="V24" s="20"/>
+      <c r="W24" s="20"/>
+      <c r="X24" s="20"/>
+      <c r="Y24" s="20"/>
+      <c r="Z24" s="20"/>
+      <c r="AA24" s="20"/>
+      <c r="AB24" s="20"/>
+      <c r="AC24" s="20"/>
+      <c r="AD24" s="20"/>
+      <c r="AE24" s="21"/>
+      <c r="AF24" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="AG24" s="24"/>
+      <c r="AH24" s="24"/>
+      <c r="AI24" s="26"/>
+      <c r="AJ24" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="AK24" s="25"/>
+      <c r="AL24" s="25"/>
+      <c r="AM24" s="25"/>
+      <c r="AN24" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="AO24" s="25"/>
+      <c r="AP24" s="25"/>
+      <c r="AQ24" s="25"/>
+    </row>
+    <row r="25" spans="3:43" x14ac:dyDescent="0.4">
+      <c r="C25" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="D25" s="20"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="20"/>
+      <c r="H25" s="20"/>
+      <c r="I25" s="20"/>
+      <c r="J25" s="20"/>
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+      <c r="M25" s="20"/>
+      <c r="N25" s="20"/>
+      <c r="O25" s="20"/>
+      <c r="P25" s="21"/>
+      <c r="Q25" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="R25" s="20"/>
+      <c r="S25" s="20"/>
+      <c r="T25" s="20"/>
+      <c r="U25" s="20"/>
+      <c r="V25" s="20"/>
+      <c r="W25" s="20"/>
+      <c r="X25" s="20"/>
+      <c r="Y25" s="20"/>
+      <c r="Z25" s="20"/>
+      <c r="AA25" s="20"/>
+      <c r="AB25" s="20"/>
+      <c r="AC25" s="20"/>
+      <c r="AD25" s="20"/>
+      <c r="AE25" s="21"/>
+      <c r="AF25" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="AG25" s="24"/>
+      <c r="AH25" s="24"/>
+      <c r="AI25" s="26"/>
+      <c r="AJ25" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="AK25" s="25"/>
+      <c r="AL25" s="25"/>
+      <c r="AM25" s="25"/>
+      <c r="AN25" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="AO25" s="25"/>
+      <c r="AP25" s="25"/>
+      <c r="AQ25" s="25"/>
+    </row>
+    <row r="26" spans="3:43" x14ac:dyDescent="0.4">
+      <c r="C26" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="20"/>
+      <c r="H26" s="20"/>
+      <c r="I26" s="20"/>
+      <c r="J26" s="20"/>
+      <c r="K26" s="20"/>
+      <c r="L26" s="20"/>
+      <c r="M26" s="20"/>
+      <c r="N26" s="20"/>
+      <c r="O26" s="20"/>
+      <c r="P26" s="21"/>
+      <c r="Q26" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="R26" s="20"/>
+      <c r="S26" s="20"/>
+      <c r="T26" s="20"/>
+      <c r="U26" s="20"/>
+      <c r="V26" s="20"/>
+      <c r="W26" s="20"/>
+      <c r="X26" s="20"/>
+      <c r="Y26" s="20"/>
+      <c r="Z26" s="20"/>
+      <c r="AA26" s="20"/>
+      <c r="AB26" s="20"/>
+      <c r="AC26" s="20"/>
+      <c r="AD26" s="20"/>
+      <c r="AE26" s="21"/>
+      <c r="AF26" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="AG26" s="25"/>
+      <c r="AH26" s="25"/>
+      <c r="AI26" s="25"/>
+      <c r="AJ26" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="AK26" s="25"/>
+      <c r="AL26" s="25"/>
+      <c r="AM26" s="25"/>
+      <c r="AN26" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="AO26" s="25"/>
+      <c r="AP26" s="25"/>
+      <c r="AQ26" s="25"/>
+    </row>
+    <row r="27" spans="3:43" x14ac:dyDescent="0.4">
+      <c r="C27" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="D27" s="20"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="20"/>
+      <c r="H27" s="20"/>
+      <c r="I27" s="20"/>
+      <c r="J27" s="20"/>
+      <c r="K27" s="20"/>
+      <c r="L27" s="20"/>
+      <c r="M27" s="20"/>
+      <c r="N27" s="20"/>
+      <c r="O27" s="20"/>
+      <c r="P27" s="21"/>
+      <c r="Q27" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="R27" s="20"/>
+      <c r="S27" s="20"/>
+      <c r="T27" s="20"/>
+      <c r="U27" s="20"/>
+      <c r="V27" s="20"/>
+      <c r="W27" s="20"/>
+      <c r="X27" s="20"/>
+      <c r="Y27" s="20"/>
+      <c r="Z27" s="20"/>
+      <c r="AA27" s="20"/>
+      <c r="AB27" s="20"/>
+      <c r="AC27" s="20"/>
+      <c r="AD27" s="20"/>
+      <c r="AE27" s="21"/>
+      <c r="AF27" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="AG27" s="25"/>
+      <c r="AH27" s="25"/>
+      <c r="AI27" s="25"/>
+      <c r="AJ27" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="AK27" s="25"/>
+      <c r="AL27" s="25"/>
+      <c r="AM27" s="25"/>
+      <c r="AN27" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="AO27" s="25"/>
+      <c r="AP27" s="25"/>
+      <c r="AQ27" s="25"/>
+    </row>
+    <row r="28" spans="3:43" x14ac:dyDescent="0.4">
+      <c r="C28" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
+      <c r="H28" s="20"/>
+      <c r="I28" s="20"/>
+      <c r="J28" s="20"/>
+      <c r="K28" s="20"/>
+      <c r="L28" s="20"/>
+      <c r="M28" s="20"/>
+      <c r="N28" s="20"/>
+      <c r="O28" s="20"/>
+      <c r="P28" s="21"/>
+      <c r="Q28" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="R28" s="20"/>
+      <c r="S28" s="20"/>
+      <c r="T28" s="20"/>
+      <c r="U28" s="20"/>
+      <c r="V28" s="20"/>
+      <c r="W28" s="20"/>
+      <c r="X28" s="20"/>
+      <c r="Y28" s="20"/>
+      <c r="Z28" s="20"/>
+      <c r="AA28" s="20"/>
+      <c r="AB28" s="20"/>
+      <c r="AC28" s="20"/>
+      <c r="AD28" s="20"/>
+      <c r="AE28" s="21"/>
+      <c r="AF28" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="AG28" s="25"/>
+      <c r="AH28" s="25"/>
+      <c r="AI28" s="25"/>
+      <c r="AJ28" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="AK28" s="25"/>
+      <c r="AL28" s="25"/>
+      <c r="AM28" s="25"/>
+      <c r="AN28" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="AO28" s="25"/>
+      <c r="AP28" s="25"/>
+      <c r="AQ28" s="25"/>
+    </row>
+    <row r="49" spans="3:3" x14ac:dyDescent="0.4">
+      <c r="C49" s="8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" ht="18.75" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B74" s="9" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.4">
+      <c r="C75" s="8" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.4">
+      <c r="D76" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E76" s="12"/>
+      <c r="F76" s="12"/>
+      <c r="G76" s="12"/>
+      <c r="H76" s="12"/>
+      <c r="I76" s="12"/>
+      <c r="J76" s="12"/>
+      <c r="K76" s="12"/>
+      <c r="L76" s="12"/>
+      <c r="M76" s="12"/>
+      <c r="N76" s="12"/>
+      <c r="O76" s="12"/>
+      <c r="P76" s="12"/>
+      <c r="Q76" s="12"/>
+      <c r="R76" s="12"/>
+      <c r="S76" s="12"/>
+      <c r="T76" s="12"/>
+      <c r="U76" s="12"/>
+      <c r="V76" s="12"/>
+      <c r="W76" s="12"/>
+      <c r="X76" s="12"/>
+      <c r="Y76" s="12"/>
+      <c r="Z76" s="12"/>
+      <c r="AA76" s="12"/>
+      <c r="AB76" s="12"/>
+      <c r="AC76" s="13"/>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.4">
+      <c r="D77" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC77" s="15"/>
+    </row>
+    <row r="78" spans="2:30" x14ac:dyDescent="0.4">
+      <c r="D78" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="AC78" s="15"/>
+      <c r="AD78" s="8" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.4">
+      <c r="D79" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="E79" s="17"/>
+      <c r="F79" s="17"/>
+      <c r="G79" s="17"/>
+      <c r="H79" s="17"/>
+      <c r="I79" s="17"/>
+      <c r="J79" s="17"/>
+      <c r="K79" s="17"/>
+      <c r="L79" s="17"/>
+      <c r="M79" s="17"/>
+      <c r="N79" s="17"/>
+      <c r="O79" s="17"/>
+      <c r="P79" s="17"/>
+      <c r="Q79" s="17"/>
+      <c r="R79" s="17"/>
+      <c r="S79" s="17"/>
+      <c r="T79" s="17"/>
+      <c r="U79" s="17"/>
+      <c r="V79" s="17"/>
+      <c r="W79" s="17"/>
+      <c r="X79" s="17"/>
+      <c r="Y79" s="17"/>
+      <c r="Z79" s="17"/>
+      <c r="AA79" s="17"/>
+      <c r="AB79" s="17"/>
+      <c r="AC79" s="18"/>
+    </row>
+    <row r="81" spans="3:32" x14ac:dyDescent="0.4">
+      <c r="C81" s="8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="82" spans="3:32" x14ac:dyDescent="0.4">
+      <c r="D82" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="E82" s="20"/>
+      <c r="F82" s="20"/>
+      <c r="G82" s="20"/>
+      <c r="H82" s="20"/>
+      <c r="I82" s="20"/>
+      <c r="J82" s="20"/>
+      <c r="K82" s="20"/>
+      <c r="L82" s="20"/>
+      <c r="M82" s="20"/>
+      <c r="N82" s="20"/>
+      <c r="O82" s="20"/>
+      <c r="P82" s="20"/>
+      <c r="Q82" s="20"/>
+      <c r="R82" s="20"/>
+      <c r="S82" s="20"/>
+      <c r="T82" s="20"/>
+      <c r="U82" s="20"/>
+      <c r="V82" s="20"/>
+      <c r="W82" s="20"/>
+      <c r="X82" s="20"/>
+      <c r="Y82" s="20"/>
+      <c r="Z82" s="20"/>
+      <c r="AA82" s="20"/>
+      <c r="AB82" s="20"/>
+      <c r="AC82" s="20"/>
+      <c r="AD82" s="20"/>
+      <c r="AE82" s="20"/>
+      <c r="AF82" s="21"/>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.4">
+      <c r="C84" s="8" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.4">
+      <c r="D85" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="E85" s="20"/>
+      <c r="F85" s="20"/>
+      <c r="G85" s="20"/>
+      <c r="H85" s="20"/>
+      <c r="I85" s="20"/>
+      <c r="J85" s="20"/>
+      <c r="K85" s="20"/>
+      <c r="L85" s="20"/>
+      <c r="M85" s="20"/>
+      <c r="N85" s="20"/>
+      <c r="O85" s="20"/>
+      <c r="P85" s="20"/>
+      <c r="Q85" s="20"/>
+      <c r="R85" s="20"/>
+      <c r="S85" s="20"/>
+      <c r="T85" s="20"/>
+      <c r="U85" s="20"/>
+      <c r="V85" s="20"/>
+      <c r="W85" s="20"/>
+      <c r="X85" s="20"/>
+      <c r="Y85" s="20"/>
+      <c r="Z85" s="20"/>
+      <c r="AA85" s="20"/>
+      <c r="AB85" s="20"/>
+      <c r="AC85" s="20"/>
+      <c r="AD85" s="20"/>
+      <c r="AE85" s="20"/>
+      <c r="AF85" s="21"/>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.4">
+      <c r="D87" s="8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="21">
+    <mergeCell ref="AN28:AQ28"/>
+    <mergeCell ref="AN22:AQ22"/>
+    <mergeCell ref="AN23:AQ23"/>
+    <mergeCell ref="AN24:AQ24"/>
+    <mergeCell ref="AN25:AQ25"/>
+    <mergeCell ref="AN26:AQ26"/>
+    <mergeCell ref="AN27:AQ27"/>
+    <mergeCell ref="AJ23:AM23"/>
+    <mergeCell ref="AJ24:AM24"/>
+    <mergeCell ref="AJ25:AM25"/>
+    <mergeCell ref="AJ26:AM26"/>
+    <mergeCell ref="AJ27:AM27"/>
+    <mergeCell ref="AJ28:AM28"/>
+    <mergeCell ref="AJ22:AM22"/>
+    <mergeCell ref="AF22:AI22"/>
+    <mergeCell ref="AF23:AI23"/>
+    <mergeCell ref="AF24:AI24"/>
+    <mergeCell ref="AF25:AI25"/>
+    <mergeCell ref="AF26:AI26"/>
+    <mergeCell ref="AF27:AI27"/>
+    <mergeCell ref="AF28:AI28"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <hyperlinks>
+    <hyperlink ref="E6" r:id="rId1" xr:uid="{F4B890BF-95BB-4F43-AB4D-73701196867E}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/調査内容/アウトプット.xlsx
+++ b/調査内容/アウトプット.xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\aaa\elkstack\調査内容\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61E89901-DC71-4E62-8714-E748C98962EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A945A13E-6CD5-4D91-99D8-64C1BC2853FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{FE37317B-BE23-49EA-9156-A5F997289FA1}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{FE37317B-BE23-49EA-9156-A5F997289FA1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId2"/>
     <sheet name="GmailでSMTP送信する設定" sheetId="4" r:id="rId3"/>
     <sheet name="GmailでSMTP送信する設定 (2)" sheetId="6" r:id="rId4"/>
+    <sheet name="Sheet2" sheetId="7" r:id="rId5"/>
+    <sheet name="Sheet2 (2)" sheetId="8" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="111">
   <si>
     <t>徐々に上昇、減少する値が一定値を超えたら</t>
     <rPh sb="0" eb="2">
@@ -754,6 +756,194 @@
     <rPh sb="3" eb="5">
       <t>テジュン</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>正常</t>
+    <rPh sb="0" eb="2">
+      <t>セイジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>異常</t>
+    <rPh sb="0" eb="2">
+      <t>イジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>急激な変化</t>
+    <rPh sb="0" eb="2">
+      <t>キュウゲキ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヘンカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>徐々な変化</t>
+    <rPh sb="0" eb="2">
+      <t>ジョジョ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヘンカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>徐々な変化から急激な変化</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>変化なし</t>
+    <rPh sb="0" eb="2">
+      <t>ヘンカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>正常範囲内で値が変化</t>
+    <rPh sb="0" eb="2">
+      <t>セイジョウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ハンイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ナイ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ヘンカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>△</t>
+  </si>
+  <si>
+    <t>△</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>なし</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>予兆検知</t>
+    <rPh sb="0" eb="2">
+      <t>ヨチョウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ケンチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>誤検知しない</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>誤検知しない
+※閾値の設定値に適切な値を入れる必要がある</t>
+    <rPh sb="8" eb="10">
+      <t>シキイチ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>チ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>アタイ</t>
+    </rPh>
+    <rPh sb="20" eb="21">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ヒツヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>誤検知しない
+振動値</t>
+    <rPh sb="0" eb="3">
+      <t>ゴケンチ</t>
+    </rPh>
+    <rPh sb="7" eb="10">
+      <t>シンドウチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>振動値 &gt;= 閾値</t>
+    <rPh sb="0" eb="3">
+      <t>シンドウチ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>シキイチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>振動値 &gt;= 閾値</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>異常スコア &gt;= 閾値</t>
+    <rPh sb="0" eb="2">
+      <t>イジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>異常スコア &gt;= 閾値</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>トレンドの下限 &gt;= 閾値</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>トレンドの下限 &gt;= 閾値</t>
+    <rPh sb="5" eb="7">
+      <t>カゲン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>強み</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>弱み</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>閾値</t>
+    <rPh sb="0" eb="2">
+      <t>シキイチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>異常スコア &gt;= 75</t>
+    <rPh sb="0" eb="2">
+      <t>イジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>異常スコア &gt;= 75</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -812,7 +1002,7 @@
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -827,6 +1017,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.749992370372631"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCCCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1021,7 +1229,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1034,119 +1242,170 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1157,6 +1416,16 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFFFFCC"/>
+      <color rgb="FFFFCCCC"/>
+      <color rgb="FFFFAAAA"/>
+      <color rgb="FFFF0000"/>
+      <color rgb="FFFF7C80"/>
+      <color rgb="FFFF5050"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1963,50 +2232,50 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:15" x14ac:dyDescent="0.4">
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
+      <c r="J3" s="42"/>
+      <c r="K3" s="42"/>
+      <c r="L3" s="42"/>
+      <c r="M3" s="42"/>
+      <c r="N3" s="42"/>
+      <c r="O3" s="42"/>
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.4">
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.4">
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.4">
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="3" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2014,16 +2283,16 @@
       <c r="B7" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="3" t="s">
         <v>34</v>
       </c>
     </row>
@@ -2031,14 +2300,14 @@
       <c r="B8" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="6"/>
-      <c r="E8" s="4" t="s">
+      <c r="D8" s="5"/>
+      <c r="E8" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="3" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2049,16 +2318,16 @@
       <c r="C9" t="s">
         <v>0</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="G9" s="4" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2066,14 +2335,14 @@
       <c r="C10" t="s">
         <v>1</v>
       </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="5" t="s">
+      <c r="D10" s="41"/>
+      <c r="E10" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="G10" s="4" t="s">
         <v>40</v>
       </c>
     </row>
@@ -2084,16 +2353,16 @@
       <c r="C11" t="s">
         <v>0</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="G11" s="4" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2101,106 +2370,106 @@
       <c r="C12" t="s">
         <v>1</v>
       </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="5" t="s">
+      <c r="D12" s="41"/>
+      <c r="E12" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="G12" s="4" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.4">
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.4">
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.4">
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.4">
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
     </row>
     <row r="17" spans="4:7" x14ac:dyDescent="0.4">
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
     </row>
     <row r="18" spans="4:7" x14ac:dyDescent="0.4">
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
     </row>
     <row r="19" spans="4:7" x14ac:dyDescent="0.4">
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
     </row>
     <row r="20" spans="4:7" x14ac:dyDescent="0.4">
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
     </row>
     <row r="21" spans="4:7" x14ac:dyDescent="0.4">
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
     </row>
     <row r="22" spans="4:7" x14ac:dyDescent="0.4">
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
     </row>
     <row r="23" spans="4:7" x14ac:dyDescent="0.4">
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
     </row>
     <row r="24" spans="4:7" x14ac:dyDescent="0.4">
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
     </row>
     <row r="25" spans="4:7" x14ac:dyDescent="0.4">
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
     </row>
     <row r="26" spans="4:7" x14ac:dyDescent="0.4">
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
     </row>
     <row r="27" spans="4:7" x14ac:dyDescent="0.4">
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -2220,213 +2489,213 @@
   <dimension ref="A1:AF86"/>
   <sheetFormatPr defaultColWidth="3.125" defaultRowHeight="15.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="16384" width="3.125" style="8"/>
+    <col min="1" max="16384" width="3.125" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="16.5" thickTop="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="1:5" ht="18.75" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="8" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="7" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="7" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.4">
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="7" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="28" spans="3:3" x14ac:dyDescent="0.4">
-      <c r="C28" s="8" t="s">
+      <c r="C28" s="7" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="48" spans="3:3" x14ac:dyDescent="0.4">
-      <c r="C48" s="8" t="s">
+      <c r="C48" s="7" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="73" spans="2:30" ht="18.75" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B73" s="9" t="s">
+      <c r="B73" s="8" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="74" spans="2:30" x14ac:dyDescent="0.4">
-      <c r="C74" s="8" t="s">
+      <c r="C74" s="7" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="75" spans="2:30" x14ac:dyDescent="0.4">
-      <c r="D75" s="11" t="s">
+      <c r="D75" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="E75" s="12"/>
-      <c r="F75" s="12"/>
-      <c r="G75" s="12"/>
-      <c r="H75" s="12"/>
-      <c r="I75" s="12"/>
-      <c r="J75" s="12"/>
-      <c r="K75" s="12"/>
-      <c r="L75" s="12"/>
-      <c r="M75" s="12"/>
-      <c r="N75" s="12"/>
-      <c r="O75" s="12"/>
-      <c r="P75" s="12"/>
-      <c r="Q75" s="12"/>
-      <c r="R75" s="12"/>
-      <c r="S75" s="12"/>
-      <c r="T75" s="12"/>
-      <c r="U75" s="12"/>
-      <c r="V75" s="12"/>
-      <c r="W75" s="12"/>
-      <c r="X75" s="12"/>
-      <c r="Y75" s="12"/>
-      <c r="Z75" s="12"/>
-      <c r="AA75" s="12"/>
-      <c r="AB75" s="12"/>
-      <c r="AC75" s="13"/>
+      <c r="E75" s="11"/>
+      <c r="F75" s="11"/>
+      <c r="G75" s="11"/>
+      <c r="H75" s="11"/>
+      <c r="I75" s="11"/>
+      <c r="J75" s="11"/>
+      <c r="K75" s="11"/>
+      <c r="L75" s="11"/>
+      <c r="M75" s="11"/>
+      <c r="N75" s="11"/>
+      <c r="O75" s="11"/>
+      <c r="P75" s="11"/>
+      <c r="Q75" s="11"/>
+      <c r="R75" s="11"/>
+      <c r="S75" s="11"/>
+      <c r="T75" s="11"/>
+      <c r="U75" s="11"/>
+      <c r="V75" s="11"/>
+      <c r="W75" s="11"/>
+      <c r="X75" s="11"/>
+      <c r="Y75" s="11"/>
+      <c r="Z75" s="11"/>
+      <c r="AA75" s="11"/>
+      <c r="AB75" s="11"/>
+      <c r="AC75" s="12"/>
     </row>
     <row r="76" spans="2:30" x14ac:dyDescent="0.4">
-      <c r="D76" s="14" t="s">
+      <c r="D76" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="AC76" s="15"/>
+      <c r="AC76" s="14"/>
     </row>
     <row r="77" spans="2:30" x14ac:dyDescent="0.4">
-      <c r="D77" s="14" t="s">
+      <c r="D77" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="AC77" s="15"/>
-      <c r="AD77" s="8" t="s">
+      <c r="AC77" s="14"/>
+      <c r="AD77" s="7" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="78" spans="2:30" x14ac:dyDescent="0.4">
-      <c r="D78" s="16" t="s">
+      <c r="D78" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="E78" s="17"/>
-      <c r="F78" s="17"/>
-      <c r="G78" s="17"/>
-      <c r="H78" s="17"/>
-      <c r="I78" s="17"/>
-      <c r="J78" s="17"/>
-      <c r="K78" s="17"/>
-      <c r="L78" s="17"/>
-      <c r="M78" s="17"/>
-      <c r="N78" s="17"/>
-      <c r="O78" s="17"/>
-      <c r="P78" s="17"/>
-      <c r="Q78" s="17"/>
-      <c r="R78" s="17"/>
-      <c r="S78" s="17"/>
-      <c r="T78" s="17"/>
-      <c r="U78" s="17"/>
-      <c r="V78" s="17"/>
-      <c r="W78" s="17"/>
-      <c r="X78" s="17"/>
-      <c r="Y78" s="17"/>
-      <c r="Z78" s="17"/>
-      <c r="AA78" s="17"/>
-      <c r="AB78" s="17"/>
-      <c r="AC78" s="18"/>
+      <c r="E78" s="16"/>
+      <c r="F78" s="16"/>
+      <c r="G78" s="16"/>
+      <c r="H78" s="16"/>
+      <c r="I78" s="16"/>
+      <c r="J78" s="16"/>
+      <c r="K78" s="16"/>
+      <c r="L78" s="16"/>
+      <c r="M78" s="16"/>
+      <c r="N78" s="16"/>
+      <c r="O78" s="16"/>
+      <c r="P78" s="16"/>
+      <c r="Q78" s="16"/>
+      <c r="R78" s="16"/>
+      <c r="S78" s="16"/>
+      <c r="T78" s="16"/>
+      <c r="U78" s="16"/>
+      <c r="V78" s="16"/>
+      <c r="W78" s="16"/>
+      <c r="X78" s="16"/>
+      <c r="Y78" s="16"/>
+      <c r="Z78" s="16"/>
+      <c r="AA78" s="16"/>
+      <c r="AB78" s="16"/>
+      <c r="AC78" s="17"/>
     </row>
     <row r="80" spans="2:30" x14ac:dyDescent="0.4">
-      <c r="C80" s="8" t="s">
+      <c r="C80" s="7" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="81" spans="3:32" x14ac:dyDescent="0.4">
-      <c r="D81" s="19" t="s">
+      <c r="D81" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="E81" s="20"/>
-      <c r="F81" s="20"/>
-      <c r="G81" s="20"/>
-      <c r="H81" s="20"/>
-      <c r="I81" s="20"/>
-      <c r="J81" s="20"/>
-      <c r="K81" s="20"/>
-      <c r="L81" s="20"/>
-      <c r="M81" s="20"/>
-      <c r="N81" s="20"/>
-      <c r="O81" s="20"/>
-      <c r="P81" s="20"/>
-      <c r="Q81" s="20"/>
-      <c r="R81" s="20"/>
-      <c r="S81" s="20"/>
-      <c r="T81" s="20"/>
-      <c r="U81" s="20"/>
-      <c r="V81" s="20"/>
-      <c r="W81" s="20"/>
-      <c r="X81" s="20"/>
-      <c r="Y81" s="20"/>
-      <c r="Z81" s="20"/>
-      <c r="AA81" s="20"/>
-      <c r="AB81" s="20"/>
-      <c r="AC81" s="20"/>
-      <c r="AD81" s="20"/>
-      <c r="AE81" s="20"/>
-      <c r="AF81" s="21"/>
+      <c r="E81" s="19"/>
+      <c r="F81" s="19"/>
+      <c r="G81" s="19"/>
+      <c r="H81" s="19"/>
+      <c r="I81" s="19"/>
+      <c r="J81" s="19"/>
+      <c r="K81" s="19"/>
+      <c r="L81" s="19"/>
+      <c r="M81" s="19"/>
+      <c r="N81" s="19"/>
+      <c r="O81" s="19"/>
+      <c r="P81" s="19"/>
+      <c r="Q81" s="19"/>
+      <c r="R81" s="19"/>
+      <c r="S81" s="19"/>
+      <c r="T81" s="19"/>
+      <c r="U81" s="19"/>
+      <c r="V81" s="19"/>
+      <c r="W81" s="19"/>
+      <c r="X81" s="19"/>
+      <c r="Y81" s="19"/>
+      <c r="Z81" s="19"/>
+      <c r="AA81" s="19"/>
+      <c r="AB81" s="19"/>
+      <c r="AC81" s="19"/>
+      <c r="AD81" s="19"/>
+      <c r="AE81" s="19"/>
+      <c r="AF81" s="20"/>
     </row>
     <row r="83" spans="3:32" x14ac:dyDescent="0.4">
-      <c r="C83" s="8" t="s">
+      <c r="C83" s="7" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="84" spans="3:32" x14ac:dyDescent="0.4">
-      <c r="D84" s="19" t="s">
+      <c r="D84" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="E84" s="20"/>
-      <c r="F84" s="20"/>
-      <c r="G84" s="20"/>
-      <c r="H84" s="20"/>
-      <c r="I84" s="20"/>
-      <c r="J84" s="20"/>
-      <c r="K84" s="20"/>
-      <c r="L84" s="20"/>
-      <c r="M84" s="20"/>
-      <c r="N84" s="20"/>
-      <c r="O84" s="20"/>
-      <c r="P84" s="20"/>
-      <c r="Q84" s="20"/>
-      <c r="R84" s="20"/>
-      <c r="S84" s="20"/>
-      <c r="T84" s="20"/>
-      <c r="U84" s="20"/>
-      <c r="V84" s="20"/>
-      <c r="W84" s="20"/>
-      <c r="X84" s="20"/>
-      <c r="Y84" s="20"/>
-      <c r="Z84" s="20"/>
-      <c r="AA84" s="20"/>
-      <c r="AB84" s="20"/>
-      <c r="AC84" s="20"/>
-      <c r="AD84" s="20"/>
-      <c r="AE84" s="20"/>
-      <c r="AF84" s="21"/>
+      <c r="E84" s="19"/>
+      <c r="F84" s="19"/>
+      <c r="G84" s="19"/>
+      <c r="H84" s="19"/>
+      <c r="I84" s="19"/>
+      <c r="J84" s="19"/>
+      <c r="K84" s="19"/>
+      <c r="L84" s="19"/>
+      <c r="M84" s="19"/>
+      <c r="N84" s="19"/>
+      <c r="O84" s="19"/>
+      <c r="P84" s="19"/>
+      <c r="Q84" s="19"/>
+      <c r="R84" s="19"/>
+      <c r="S84" s="19"/>
+      <c r="T84" s="19"/>
+      <c r="U84" s="19"/>
+      <c r="V84" s="19"/>
+      <c r="W84" s="19"/>
+      <c r="X84" s="19"/>
+      <c r="Y84" s="19"/>
+      <c r="Z84" s="19"/>
+      <c r="AA84" s="19"/>
+      <c r="AB84" s="19"/>
+      <c r="AC84" s="19"/>
+      <c r="AD84" s="19"/>
+      <c r="AE84" s="19"/>
+      <c r="AF84" s="20"/>
     </row>
     <row r="86" spans="3:32" x14ac:dyDescent="0.4">
-      <c r="D86" s="8" t="s">
+      <c r="D86" s="7" t="s">
         <v>60</v>
       </c>
     </row>
@@ -2445,749 +2714,737 @@
   <dimension ref="A1:BC87"/>
   <sheetFormatPr defaultColWidth="3.125" defaultRowHeight="15.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="16384" width="3.125" style="8"/>
+    <col min="1" max="16384" width="3.125" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:55" ht="21" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:55" ht="16.5" thickTop="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="1:55" ht="18.75" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="8" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:55" x14ac:dyDescent="0.4">
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="7" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:55" x14ac:dyDescent="0.4">
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="7" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:55" ht="18.75" x14ac:dyDescent="0.4">
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="9" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:55" ht="18.75" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="BC10" s="22"/>
+      <c r="BC10" s="21"/>
     </row>
     <row r="15" spans="1:55" ht="18.75" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="8" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="17" spans="3:43" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="3:43" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="19" spans="3:43" x14ac:dyDescent="0.4">
-      <c r="C19" s="27" t="s">
+      <c r="C19" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="28"/>
-      <c r="I19" s="28"/>
-      <c r="J19" s="28"/>
-      <c r="K19" s="28"/>
-      <c r="L19" s="28"/>
-      <c r="M19" s="28"/>
-      <c r="N19" s="28"/>
-      <c r="O19" s="28"/>
-      <c r="P19" s="29"/>
-      <c r="Q19" s="27" t="s">
+      <c r="D19" s="23"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="23"/>
+      <c r="I19" s="23"/>
+      <c r="J19" s="23"/>
+      <c r="K19" s="23"/>
+      <c r="L19" s="23"/>
+      <c r="M19" s="23"/>
+      <c r="N19" s="23"/>
+      <c r="O19" s="23"/>
+      <c r="P19" s="24"/>
+      <c r="Q19" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="R19" s="28"/>
-      <c r="S19" s="28"/>
-      <c r="T19" s="28"/>
-      <c r="U19" s="28"/>
-      <c r="V19" s="28"/>
-      <c r="W19" s="28"/>
-      <c r="X19" s="28"/>
-      <c r="Y19" s="28"/>
-      <c r="Z19" s="28"/>
-      <c r="AA19" s="28"/>
-      <c r="AB19" s="28"/>
-      <c r="AC19" s="28"/>
-      <c r="AD19" s="28"/>
-      <c r="AE19" s="29"/>
-      <c r="AF19" s="30" t="s">
+      <c r="R19" s="23"/>
+      <c r="S19" s="23"/>
+      <c r="T19" s="23"/>
+      <c r="U19" s="23"/>
+      <c r="V19" s="23"/>
+      <c r="W19" s="23"/>
+      <c r="X19" s="23"/>
+      <c r="Y19" s="23"/>
+      <c r="Z19" s="23"/>
+      <c r="AA19" s="23"/>
+      <c r="AB19" s="23"/>
+      <c r="AC19" s="23"/>
+      <c r="AD19" s="23"/>
+      <c r="AE19" s="24"/>
+      <c r="AF19" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="AG19" s="31"/>
-      <c r="AH19" s="31"/>
-      <c r="AI19" s="31"/>
-      <c r="AJ19" s="31"/>
-      <c r="AK19" s="31"/>
-      <c r="AL19" s="31"/>
-      <c r="AM19" s="31"/>
-      <c r="AN19" s="31"/>
-      <c r="AO19" s="31"/>
-      <c r="AP19" s="31"/>
-      <c r="AQ19" s="32"/>
+      <c r="AG19" s="26"/>
+      <c r="AH19" s="26"/>
+      <c r="AI19" s="26"/>
+      <c r="AJ19" s="26"/>
+      <c r="AK19" s="26"/>
+      <c r="AL19" s="26"/>
+      <c r="AM19" s="26"/>
+      <c r="AN19" s="26"/>
+      <c r="AO19" s="26"/>
+      <c r="AP19" s="26"/>
+      <c r="AQ19" s="27"/>
     </row>
     <row r="20" spans="3:43" x14ac:dyDescent="0.4">
-      <c r="C20" s="33"/>
-      <c r="D20" s="34"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="34"/>
-      <c r="H20" s="34"/>
-      <c r="I20" s="34"/>
-      <c r="J20" s="34"/>
-      <c r="K20" s="34"/>
-      <c r="L20" s="34"/>
-      <c r="M20" s="34"/>
-      <c r="N20" s="34"/>
-      <c r="O20" s="34"/>
-      <c r="P20" s="35"/>
-      <c r="Q20" s="33"/>
-      <c r="R20" s="34"/>
-      <c r="S20" s="34"/>
-      <c r="T20" s="34"/>
-      <c r="U20" s="34"/>
-      <c r="V20" s="34"/>
-      <c r="W20" s="34"/>
-      <c r="X20" s="34"/>
-      <c r="Y20" s="34"/>
-      <c r="Z20" s="34"/>
-      <c r="AA20" s="34"/>
-      <c r="AB20" s="34"/>
-      <c r="AC20" s="34"/>
-      <c r="AD20" s="34"/>
-      <c r="AE20" s="35"/>
-      <c r="AF20" s="27" t="s">
+      <c r="C20" s="28"/>
+      <c r="D20" s="29"/>
+      <c r="E20" s="29"/>
+      <c r="F20" s="29"/>
+      <c r="G20" s="29"/>
+      <c r="H20" s="29"/>
+      <c r="I20" s="29"/>
+      <c r="J20" s="29"/>
+      <c r="K20" s="29"/>
+      <c r="L20" s="29"/>
+      <c r="M20" s="29"/>
+      <c r="N20" s="29"/>
+      <c r="O20" s="29"/>
+      <c r="P20" s="30"/>
+      <c r="Q20" s="28"/>
+      <c r="R20" s="29"/>
+      <c r="S20" s="29"/>
+      <c r="T20" s="29"/>
+      <c r="U20" s="29"/>
+      <c r="V20" s="29"/>
+      <c r="W20" s="29"/>
+      <c r="X20" s="29"/>
+      <c r="Y20" s="29"/>
+      <c r="Z20" s="29"/>
+      <c r="AA20" s="29"/>
+      <c r="AB20" s="29"/>
+      <c r="AC20" s="29"/>
+      <c r="AD20" s="29"/>
+      <c r="AE20" s="30"/>
+      <c r="AF20" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="AG20" s="28"/>
-      <c r="AH20" s="28"/>
-      <c r="AI20" s="29"/>
-      <c r="AJ20" s="27" t="s">
+      <c r="AG20" s="23"/>
+      <c r="AH20" s="23"/>
+      <c r="AI20" s="24"/>
+      <c r="AJ20" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="AK20" s="28"/>
-      <c r="AL20" s="28"/>
-      <c r="AM20" s="29"/>
-      <c r="AN20" s="27" t="s">
+      <c r="AK20" s="23"/>
+      <c r="AL20" s="23"/>
+      <c r="AM20" s="24"/>
+      <c r="AN20" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="AO20" s="28"/>
-      <c r="AP20" s="28"/>
-      <c r="AQ20" s="29"/>
+      <c r="AO20" s="23"/>
+      <c r="AP20" s="23"/>
+      <c r="AQ20" s="24"/>
     </row>
     <row r="21" spans="3:43" x14ac:dyDescent="0.4">
-      <c r="C21" s="36"/>
-      <c r="D21" s="37"/>
-      <c r="E21" s="37"/>
-      <c r="F21" s="37"/>
-      <c r="G21" s="37"/>
-      <c r="H21" s="37"/>
-      <c r="I21" s="37"/>
-      <c r="J21" s="37"/>
-      <c r="K21" s="37"/>
-      <c r="L21" s="37"/>
-      <c r="M21" s="37"/>
-      <c r="N21" s="37"/>
-      <c r="O21" s="37"/>
-      <c r="P21" s="38"/>
-      <c r="Q21" s="36"/>
-      <c r="R21" s="37"/>
-      <c r="S21" s="37"/>
-      <c r="T21" s="37"/>
-      <c r="U21" s="37"/>
-      <c r="V21" s="37"/>
-      <c r="W21" s="37"/>
-      <c r="X21" s="37"/>
-      <c r="Y21" s="37"/>
-      <c r="Z21" s="37"/>
-      <c r="AA21" s="37"/>
-      <c r="AB21" s="37"/>
-      <c r="AC21" s="37"/>
-      <c r="AD21" s="37"/>
-      <c r="AE21" s="38"/>
-      <c r="AF21" s="39"/>
-      <c r="AG21" s="40"/>
-      <c r="AH21" s="40"/>
-      <c r="AI21" s="41"/>
-      <c r="AJ21" s="39" t="s">
+      <c r="C21" s="31"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="32"/>
+      <c r="I21" s="32"/>
+      <c r="J21" s="32"/>
+      <c r="K21" s="32"/>
+      <c r="L21" s="32"/>
+      <c r="M21" s="32"/>
+      <c r="N21" s="32"/>
+      <c r="O21" s="32"/>
+      <c r="P21" s="33"/>
+      <c r="Q21" s="31"/>
+      <c r="R21" s="32"/>
+      <c r="S21" s="32"/>
+      <c r="T21" s="32"/>
+      <c r="U21" s="32"/>
+      <c r="V21" s="32"/>
+      <c r="W21" s="32"/>
+      <c r="X21" s="32"/>
+      <c r="Y21" s="32"/>
+      <c r="Z21" s="32"/>
+      <c r="AA21" s="32"/>
+      <c r="AB21" s="32"/>
+      <c r="AC21" s="32"/>
+      <c r="AD21" s="32"/>
+      <c r="AE21" s="33"/>
+      <c r="AF21" s="34"/>
+      <c r="AG21" s="35"/>
+      <c r="AH21" s="35"/>
+      <c r="AI21" s="36"/>
+      <c r="AJ21" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="AK21" s="40"/>
-      <c r="AL21" s="40"/>
-      <c r="AM21" s="38"/>
-      <c r="AN21" s="39" t="s">
+      <c r="AK21" s="35"/>
+      <c r="AL21" s="35"/>
+      <c r="AM21" s="33"/>
+      <c r="AN21" s="34" t="s">
         <v>77</v>
       </c>
-      <c r="AO21" s="40"/>
-      <c r="AP21" s="40"/>
-      <c r="AQ21" s="41"/>
+      <c r="AO21" s="35"/>
+      <c r="AP21" s="35"/>
+      <c r="AQ21" s="36"/>
     </row>
     <row r="22" spans="3:43" x14ac:dyDescent="0.4">
-      <c r="C22" s="19" t="s">
+      <c r="C22" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="F22" s="20"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="20"/>
-      <c r="I22" s="20"/>
-      <c r="J22" s="20"/>
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
-      <c r="M22" s="20"/>
-      <c r="N22" s="20"/>
-      <c r="O22" s="20"/>
-      <c r="P22" s="21"/>
-      <c r="Q22" s="19" t="s">
+      <c r="D22" s="19"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="19"/>
+      <c r="I22" s="19"/>
+      <c r="J22" s="19"/>
+      <c r="K22" s="19"/>
+      <c r="L22" s="19"/>
+      <c r="M22" s="19"/>
+      <c r="N22" s="19"/>
+      <c r="O22" s="19"/>
+      <c r="P22" s="20"/>
+      <c r="Q22" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="R22" s="20"/>
-      <c r="S22" s="20"/>
-      <c r="T22" s="20"/>
-      <c r="U22" s="20"/>
-      <c r="V22" s="20"/>
-      <c r="W22" s="20"/>
-      <c r="X22" s="20"/>
-      <c r="Y22" s="20"/>
-      <c r="Z22" s="20"/>
-      <c r="AA22" s="20"/>
-      <c r="AB22" s="20"/>
-      <c r="AC22" s="20"/>
-      <c r="AD22" s="20"/>
-      <c r="AE22" s="21"/>
-      <c r="AF22" s="23" t="s">
+      <c r="R22" s="19"/>
+      <c r="S22" s="19"/>
+      <c r="T22" s="19"/>
+      <c r="U22" s="19"/>
+      <c r="V22" s="19"/>
+      <c r="W22" s="19"/>
+      <c r="X22" s="19"/>
+      <c r="Y22" s="19"/>
+      <c r="Z22" s="19"/>
+      <c r="AA22" s="19"/>
+      <c r="AB22" s="19"/>
+      <c r="AC22" s="19"/>
+      <c r="AD22" s="19"/>
+      <c r="AE22" s="20"/>
+      <c r="AF22" s="38" t="s">
         <v>81</v>
       </c>
-      <c r="AG22" s="24"/>
-      <c r="AH22" s="24"/>
-      <c r="AI22" s="26"/>
-      <c r="AJ22" s="25" t="s">
+      <c r="AG22" s="39"/>
+      <c r="AH22" s="39"/>
+      <c r="AI22" s="40"/>
+      <c r="AJ22" s="37" t="s">
         <v>81</v>
       </c>
-      <c r="AK22" s="25"/>
-      <c r="AL22" s="25"/>
-      <c r="AM22" s="25"/>
-      <c r="AN22" s="25" t="s">
+      <c r="AK22" s="37"/>
+      <c r="AL22" s="37"/>
+      <c r="AM22" s="37"/>
+      <c r="AN22" s="37" t="s">
         <v>81</v>
       </c>
-      <c r="AO22" s="25"/>
-      <c r="AP22" s="25"/>
-      <c r="AQ22" s="25"/>
+      <c r="AO22" s="37"/>
+      <c r="AP22" s="37"/>
+      <c r="AQ22" s="37"/>
     </row>
     <row r="23" spans="3:43" x14ac:dyDescent="0.4">
-      <c r="C23" s="19" t="s">
+      <c r="C23" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="D23" s="20"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="20"/>
-      <c r="I23" s="20"/>
-      <c r="J23" s="20"/>
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
-      <c r="M23" s="20"/>
-      <c r="N23" s="20"/>
-      <c r="O23" s="20"/>
-      <c r="P23" s="21"/>
-      <c r="Q23" s="19" t="s">
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="19"/>
+      <c r="J23" s="19"/>
+      <c r="K23" s="19"/>
+      <c r="L23" s="19"/>
+      <c r="M23" s="19"/>
+      <c r="N23" s="19"/>
+      <c r="O23" s="19"/>
+      <c r="P23" s="20"/>
+      <c r="Q23" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="R23" s="20"/>
-      <c r="S23" s="20"/>
-      <c r="T23" s="20"/>
-      <c r="U23" s="20"/>
-      <c r="V23" s="20"/>
-      <c r="W23" s="20"/>
-      <c r="X23" s="20"/>
-      <c r="Y23" s="20"/>
-      <c r="Z23" s="20"/>
-      <c r="AA23" s="20"/>
-      <c r="AB23" s="20"/>
-      <c r="AC23" s="20"/>
-      <c r="AD23" s="20"/>
-      <c r="AE23" s="21"/>
-      <c r="AF23" s="23" t="s">
+      <c r="R23" s="19"/>
+      <c r="S23" s="19"/>
+      <c r="T23" s="19"/>
+      <c r="U23" s="19"/>
+      <c r="V23" s="19"/>
+      <c r="W23" s="19"/>
+      <c r="X23" s="19"/>
+      <c r="Y23" s="19"/>
+      <c r="Z23" s="19"/>
+      <c r="AA23" s="19"/>
+      <c r="AB23" s="19"/>
+      <c r="AC23" s="19"/>
+      <c r="AD23" s="19"/>
+      <c r="AE23" s="20"/>
+      <c r="AF23" s="38" t="s">
         <v>82</v>
       </c>
-      <c r="AG23" s="24"/>
-      <c r="AH23" s="24"/>
-      <c r="AI23" s="26"/>
-      <c r="AJ23" s="25" t="s">
+      <c r="AG23" s="39"/>
+      <c r="AH23" s="39"/>
+      <c r="AI23" s="40"/>
+      <c r="AJ23" s="37" t="s">
         <v>81</v>
       </c>
-      <c r="AK23" s="25"/>
-      <c r="AL23" s="25"/>
-      <c r="AM23" s="25"/>
-      <c r="AN23" s="25" t="s">
+      <c r="AK23" s="37"/>
+      <c r="AL23" s="37"/>
+      <c r="AM23" s="37"/>
+      <c r="AN23" s="37" t="s">
         <v>81</v>
       </c>
-      <c r="AO23" s="25"/>
-      <c r="AP23" s="25"/>
-      <c r="AQ23" s="25"/>
+      <c r="AO23" s="37"/>
+      <c r="AP23" s="37"/>
+      <c r="AQ23" s="37"/>
     </row>
     <row r="24" spans="3:43" x14ac:dyDescent="0.4">
-      <c r="C24" s="19" t="s">
+      <c r="C24" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="20"/>
-      <c r="H24" s="20"/>
-      <c r="I24" s="20"/>
-      <c r="J24" s="20"/>
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
-      <c r="M24" s="20"/>
-      <c r="N24" s="20"/>
-      <c r="O24" s="20"/>
-      <c r="P24" s="21"/>
-      <c r="Q24" s="19" t="s">
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="19"/>
+      <c r="J24" s="19"/>
+      <c r="K24" s="19"/>
+      <c r="L24" s="19"/>
+      <c r="M24" s="19"/>
+      <c r="N24" s="19"/>
+      <c r="O24" s="19"/>
+      <c r="P24" s="20"/>
+      <c r="Q24" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="R24" s="20"/>
-      <c r="S24" s="20"/>
-      <c r="T24" s="20"/>
-      <c r="U24" s="20"/>
-      <c r="V24" s="20"/>
-      <c r="W24" s="20"/>
-      <c r="X24" s="20"/>
-      <c r="Y24" s="20"/>
-      <c r="Z24" s="20"/>
-      <c r="AA24" s="20"/>
-      <c r="AB24" s="20"/>
-      <c r="AC24" s="20"/>
-      <c r="AD24" s="20"/>
-      <c r="AE24" s="21"/>
-      <c r="AF24" s="23" t="s">
+      <c r="R24" s="19"/>
+      <c r="S24" s="19"/>
+      <c r="T24" s="19"/>
+      <c r="U24" s="19"/>
+      <c r="V24" s="19"/>
+      <c r="W24" s="19"/>
+      <c r="X24" s="19"/>
+      <c r="Y24" s="19"/>
+      <c r="Z24" s="19"/>
+      <c r="AA24" s="19"/>
+      <c r="AB24" s="19"/>
+      <c r="AC24" s="19"/>
+      <c r="AD24" s="19"/>
+      <c r="AE24" s="20"/>
+      <c r="AF24" s="38" t="s">
         <v>82</v>
       </c>
-      <c r="AG24" s="24"/>
-      <c r="AH24" s="24"/>
-      <c r="AI24" s="26"/>
-      <c r="AJ24" s="25" t="s">
+      <c r="AG24" s="39"/>
+      <c r="AH24" s="39"/>
+      <c r="AI24" s="40"/>
+      <c r="AJ24" s="37" t="s">
         <v>81</v>
       </c>
-      <c r="AK24" s="25"/>
-      <c r="AL24" s="25"/>
-      <c r="AM24" s="25"/>
-      <c r="AN24" s="25" t="s">
+      <c r="AK24" s="37"/>
+      <c r="AL24" s="37"/>
+      <c r="AM24" s="37"/>
+      <c r="AN24" s="37" t="s">
         <v>81</v>
       </c>
-      <c r="AO24" s="25"/>
-      <c r="AP24" s="25"/>
-      <c r="AQ24" s="25"/>
+      <c r="AO24" s="37"/>
+      <c r="AP24" s="37"/>
+      <c r="AQ24" s="37"/>
     </row>
     <row r="25" spans="3:43" x14ac:dyDescent="0.4">
-      <c r="C25" s="19" t="s">
+      <c r="C25" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="20"/>
-      <c r="I25" s="20"/>
-      <c r="J25" s="20"/>
-      <c r="K25" s="20"/>
-      <c r="L25" s="20"/>
-      <c r="M25" s="20"/>
-      <c r="N25" s="20"/>
-      <c r="O25" s="20"/>
-      <c r="P25" s="21"/>
-      <c r="Q25" s="19" t="s">
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="19"/>
+      <c r="L25" s="19"/>
+      <c r="M25" s="19"/>
+      <c r="N25" s="19"/>
+      <c r="O25" s="19"/>
+      <c r="P25" s="20"/>
+      <c r="Q25" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="R25" s="20"/>
-      <c r="S25" s="20"/>
-      <c r="T25" s="20"/>
-      <c r="U25" s="20"/>
-      <c r="V25" s="20"/>
-      <c r="W25" s="20"/>
-      <c r="X25" s="20"/>
-      <c r="Y25" s="20"/>
-      <c r="Z25" s="20"/>
-      <c r="AA25" s="20"/>
-      <c r="AB25" s="20"/>
-      <c r="AC25" s="20"/>
-      <c r="AD25" s="20"/>
-      <c r="AE25" s="21"/>
-      <c r="AF25" s="23" t="s">
+      <c r="R25" s="19"/>
+      <c r="S25" s="19"/>
+      <c r="T25" s="19"/>
+      <c r="U25" s="19"/>
+      <c r="V25" s="19"/>
+      <c r="W25" s="19"/>
+      <c r="X25" s="19"/>
+      <c r="Y25" s="19"/>
+      <c r="Z25" s="19"/>
+      <c r="AA25" s="19"/>
+      <c r="AB25" s="19"/>
+      <c r="AC25" s="19"/>
+      <c r="AD25" s="19"/>
+      <c r="AE25" s="20"/>
+      <c r="AF25" s="38" t="s">
         <v>82</v>
       </c>
-      <c r="AG25" s="24"/>
-      <c r="AH25" s="24"/>
-      <c r="AI25" s="26"/>
-      <c r="AJ25" s="25" t="s">
+      <c r="AG25" s="39"/>
+      <c r="AH25" s="39"/>
+      <c r="AI25" s="40"/>
+      <c r="AJ25" s="37" t="s">
         <v>81</v>
       </c>
-      <c r="AK25" s="25"/>
-      <c r="AL25" s="25"/>
-      <c r="AM25" s="25"/>
-      <c r="AN25" s="25" t="s">
+      <c r="AK25" s="37"/>
+      <c r="AL25" s="37"/>
+      <c r="AM25" s="37"/>
+      <c r="AN25" s="37" t="s">
         <v>81</v>
       </c>
-      <c r="AO25" s="25"/>
-      <c r="AP25" s="25"/>
-      <c r="AQ25" s="25"/>
+      <c r="AO25" s="37"/>
+      <c r="AP25" s="37"/>
+      <c r="AQ25" s="37"/>
     </row>
     <row r="26" spans="3:43" x14ac:dyDescent="0.4">
-      <c r="C26" s="19" t="s">
+      <c r="C26" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="20"/>
-      <c r="I26" s="20"/>
-      <c r="J26" s="20"/>
-      <c r="K26" s="20"/>
-      <c r="L26" s="20"/>
-      <c r="M26" s="20"/>
-      <c r="N26" s="20"/>
-      <c r="O26" s="20"/>
-      <c r="P26" s="21"/>
-      <c r="Q26" s="19" t="s">
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="19"/>
+      <c r="K26" s="19"/>
+      <c r="L26" s="19"/>
+      <c r="M26" s="19"/>
+      <c r="N26" s="19"/>
+      <c r="O26" s="19"/>
+      <c r="P26" s="20"/>
+      <c r="Q26" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="R26" s="20"/>
-      <c r="S26" s="20"/>
-      <c r="T26" s="20"/>
-      <c r="U26" s="20"/>
-      <c r="V26" s="20"/>
-      <c r="W26" s="20"/>
-      <c r="X26" s="20"/>
-      <c r="Y26" s="20"/>
-      <c r="Z26" s="20"/>
-      <c r="AA26" s="20"/>
-      <c r="AB26" s="20"/>
-      <c r="AC26" s="20"/>
-      <c r="AD26" s="20"/>
-      <c r="AE26" s="21"/>
-      <c r="AF26" s="25" t="s">
+      <c r="R26" s="19"/>
+      <c r="S26" s="19"/>
+      <c r="T26" s="19"/>
+      <c r="U26" s="19"/>
+      <c r="V26" s="19"/>
+      <c r="W26" s="19"/>
+      <c r="X26" s="19"/>
+      <c r="Y26" s="19"/>
+      <c r="Z26" s="19"/>
+      <c r="AA26" s="19"/>
+      <c r="AB26" s="19"/>
+      <c r="AC26" s="19"/>
+      <c r="AD26" s="19"/>
+      <c r="AE26" s="20"/>
+      <c r="AF26" s="37" t="s">
         <v>81</v>
       </c>
-      <c r="AG26" s="25"/>
-      <c r="AH26" s="25"/>
-      <c r="AI26" s="25"/>
-      <c r="AJ26" s="25" t="s">
+      <c r="AG26" s="37"/>
+      <c r="AH26" s="37"/>
+      <c r="AI26" s="37"/>
+      <c r="AJ26" s="37" t="s">
         <v>81</v>
       </c>
-      <c r="AK26" s="25"/>
-      <c r="AL26" s="25"/>
-      <c r="AM26" s="25"/>
-      <c r="AN26" s="25" t="s">
+      <c r="AK26" s="37"/>
+      <c r="AL26" s="37"/>
+      <c r="AM26" s="37"/>
+      <c r="AN26" s="37" t="s">
         <v>81</v>
       </c>
-      <c r="AO26" s="25"/>
-      <c r="AP26" s="25"/>
-      <c r="AQ26" s="25"/>
+      <c r="AO26" s="37"/>
+      <c r="AP26" s="37"/>
+      <c r="AQ26" s="37"/>
     </row>
     <row r="27" spans="3:43" x14ac:dyDescent="0.4">
-      <c r="C27" s="19" t="s">
+      <c r="C27" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="D27" s="20"/>
-      <c r="E27" s="20"/>
-      <c r="F27" s="20"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="20"/>
-      <c r="I27" s="20"/>
-      <c r="J27" s="20"/>
-      <c r="K27" s="20"/>
-      <c r="L27" s="20"/>
-      <c r="M27" s="20"/>
-      <c r="N27" s="20"/>
-      <c r="O27" s="20"/>
-      <c r="P27" s="21"/>
-      <c r="Q27" s="19" t="s">
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="19"/>
+      <c r="K27" s="19"/>
+      <c r="L27" s="19"/>
+      <c r="M27" s="19"/>
+      <c r="N27" s="19"/>
+      <c r="O27" s="19"/>
+      <c r="P27" s="20"/>
+      <c r="Q27" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="R27" s="20"/>
-      <c r="S27" s="20"/>
-      <c r="T27" s="20"/>
-      <c r="U27" s="20"/>
-      <c r="V27" s="20"/>
-      <c r="W27" s="20"/>
-      <c r="X27" s="20"/>
-      <c r="Y27" s="20"/>
-      <c r="Z27" s="20"/>
-      <c r="AA27" s="20"/>
-      <c r="AB27" s="20"/>
-      <c r="AC27" s="20"/>
-      <c r="AD27" s="20"/>
-      <c r="AE27" s="21"/>
-      <c r="AF27" s="25" t="s">
+      <c r="R27" s="19"/>
+      <c r="S27" s="19"/>
+      <c r="T27" s="19"/>
+      <c r="U27" s="19"/>
+      <c r="V27" s="19"/>
+      <c r="W27" s="19"/>
+      <c r="X27" s="19"/>
+      <c r="Y27" s="19"/>
+      <c r="Z27" s="19"/>
+      <c r="AA27" s="19"/>
+      <c r="AB27" s="19"/>
+      <c r="AC27" s="19"/>
+      <c r="AD27" s="19"/>
+      <c r="AE27" s="20"/>
+      <c r="AF27" s="37" t="s">
         <v>81</v>
       </c>
-      <c r="AG27" s="25"/>
-      <c r="AH27" s="25"/>
-      <c r="AI27" s="25"/>
-      <c r="AJ27" s="25" t="s">
+      <c r="AG27" s="37"/>
+      <c r="AH27" s="37"/>
+      <c r="AI27" s="37"/>
+      <c r="AJ27" s="37" t="s">
         <v>81</v>
       </c>
-      <c r="AK27" s="25"/>
-      <c r="AL27" s="25"/>
-      <c r="AM27" s="25"/>
-      <c r="AN27" s="25" t="s">
+      <c r="AK27" s="37"/>
+      <c r="AL27" s="37"/>
+      <c r="AM27" s="37"/>
+      <c r="AN27" s="37" t="s">
         <v>81</v>
       </c>
-      <c r="AO27" s="25"/>
-      <c r="AP27" s="25"/>
-      <c r="AQ27" s="25"/>
+      <c r="AO27" s="37"/>
+      <c r="AP27" s="37"/>
+      <c r="AQ27" s="37"/>
     </row>
     <row r="28" spans="3:43" x14ac:dyDescent="0.4">
-      <c r="C28" s="19" t="s">
+      <c r="C28" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="20"/>
-      <c r="I28" s="20"/>
-      <c r="J28" s="20"/>
-      <c r="K28" s="20"/>
-      <c r="L28" s="20"/>
-      <c r="M28" s="20"/>
-      <c r="N28" s="20"/>
-      <c r="O28" s="20"/>
-      <c r="P28" s="21"/>
-      <c r="Q28" s="19" t="s">
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="19"/>
+      <c r="K28" s="19"/>
+      <c r="L28" s="19"/>
+      <c r="M28" s="19"/>
+      <c r="N28" s="19"/>
+      <c r="O28" s="19"/>
+      <c r="P28" s="20"/>
+      <c r="Q28" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="R28" s="20"/>
-      <c r="S28" s="20"/>
-      <c r="T28" s="20"/>
-      <c r="U28" s="20"/>
-      <c r="V28" s="20"/>
-      <c r="W28" s="20"/>
-      <c r="X28" s="20"/>
-      <c r="Y28" s="20"/>
-      <c r="Z28" s="20"/>
-      <c r="AA28" s="20"/>
-      <c r="AB28" s="20"/>
-      <c r="AC28" s="20"/>
-      <c r="AD28" s="20"/>
-      <c r="AE28" s="21"/>
-      <c r="AF28" s="25" t="s">
+      <c r="R28" s="19"/>
+      <c r="S28" s="19"/>
+      <c r="T28" s="19"/>
+      <c r="U28" s="19"/>
+      <c r="V28" s="19"/>
+      <c r="W28" s="19"/>
+      <c r="X28" s="19"/>
+      <c r="Y28" s="19"/>
+      <c r="Z28" s="19"/>
+      <c r="AA28" s="19"/>
+      <c r="AB28" s="19"/>
+      <c r="AC28" s="19"/>
+      <c r="AD28" s="19"/>
+      <c r="AE28" s="20"/>
+      <c r="AF28" s="37" t="s">
         <v>81</v>
       </c>
-      <c r="AG28" s="25"/>
-      <c r="AH28" s="25"/>
-      <c r="AI28" s="25"/>
-      <c r="AJ28" s="25" t="s">
+      <c r="AG28" s="37"/>
+      <c r="AH28" s="37"/>
+      <c r="AI28" s="37"/>
+      <c r="AJ28" s="37" t="s">
         <v>81</v>
       </c>
-      <c r="AK28" s="25"/>
-      <c r="AL28" s="25"/>
-      <c r="AM28" s="25"/>
-      <c r="AN28" s="25" t="s">
+      <c r="AK28" s="37"/>
+      <c r="AL28" s="37"/>
+      <c r="AM28" s="37"/>
+      <c r="AN28" s="37" t="s">
         <v>81</v>
       </c>
-      <c r="AO28" s="25"/>
-      <c r="AP28" s="25"/>
-      <c r="AQ28" s="25"/>
+      <c r="AO28" s="37"/>
+      <c r="AP28" s="37"/>
+      <c r="AQ28" s="37"/>
     </row>
     <row r="49" spans="3:3" x14ac:dyDescent="0.4">
-      <c r="C49" s="8" t="s">
+      <c r="C49" s="7" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="74" spans="2:30" ht="18.75" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B74" s="9" t="s">
+      <c r="B74" s="8" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="75" spans="2:30" x14ac:dyDescent="0.4">
-      <c r="C75" s="8" t="s">
+      <c r="C75" s="7" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="76" spans="2:30" x14ac:dyDescent="0.4">
-      <c r="D76" s="11" t="s">
+      <c r="D76" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="E76" s="12"/>
-      <c r="F76" s="12"/>
-      <c r="G76" s="12"/>
-      <c r="H76" s="12"/>
-      <c r="I76" s="12"/>
-      <c r="J76" s="12"/>
-      <c r="K76" s="12"/>
-      <c r="L76" s="12"/>
-      <c r="M76" s="12"/>
-      <c r="N76" s="12"/>
-      <c r="O76" s="12"/>
-      <c r="P76" s="12"/>
-      <c r="Q76" s="12"/>
-      <c r="R76" s="12"/>
-      <c r="S76" s="12"/>
-      <c r="T76" s="12"/>
-      <c r="U76" s="12"/>
-      <c r="V76" s="12"/>
-      <c r="W76" s="12"/>
-      <c r="X76" s="12"/>
-      <c r="Y76" s="12"/>
-      <c r="Z76" s="12"/>
-      <c r="AA76" s="12"/>
-      <c r="AB76" s="12"/>
-      <c r="AC76" s="13"/>
+      <c r="E76" s="11"/>
+      <c r="F76" s="11"/>
+      <c r="G76" s="11"/>
+      <c r="H76" s="11"/>
+      <c r="I76" s="11"/>
+      <c r="J76" s="11"/>
+      <c r="K76" s="11"/>
+      <c r="L76" s="11"/>
+      <c r="M76" s="11"/>
+      <c r="N76" s="11"/>
+      <c r="O76" s="11"/>
+      <c r="P76" s="11"/>
+      <c r="Q76" s="11"/>
+      <c r="R76" s="11"/>
+      <c r="S76" s="11"/>
+      <c r="T76" s="11"/>
+      <c r="U76" s="11"/>
+      <c r="V76" s="11"/>
+      <c r="W76" s="11"/>
+      <c r="X76" s="11"/>
+      <c r="Y76" s="11"/>
+      <c r="Z76" s="11"/>
+      <c r="AA76" s="11"/>
+      <c r="AB76" s="11"/>
+      <c r="AC76" s="12"/>
     </row>
     <row r="77" spans="2:30" x14ac:dyDescent="0.4">
-      <c r="D77" s="14" t="s">
+      <c r="D77" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="AC77" s="15"/>
+      <c r="AC77" s="14"/>
     </row>
     <row r="78" spans="2:30" x14ac:dyDescent="0.4">
-      <c r="D78" s="14" t="s">
+      <c r="D78" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="AC78" s="15"/>
-      <c r="AD78" s="8" t="s">
+      <c r="AC78" s="14"/>
+      <c r="AD78" s="7" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="79" spans="2:30" x14ac:dyDescent="0.4">
-      <c r="D79" s="16" t="s">
+      <c r="D79" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="E79" s="17"/>
-      <c r="F79" s="17"/>
-      <c r="G79" s="17"/>
-      <c r="H79" s="17"/>
-      <c r="I79" s="17"/>
-      <c r="J79" s="17"/>
-      <c r="K79" s="17"/>
-      <c r="L79" s="17"/>
-      <c r="M79" s="17"/>
-      <c r="N79" s="17"/>
-      <c r="O79" s="17"/>
-      <c r="P79" s="17"/>
-      <c r="Q79" s="17"/>
-      <c r="R79" s="17"/>
-      <c r="S79" s="17"/>
-      <c r="T79" s="17"/>
-      <c r="U79" s="17"/>
-      <c r="V79" s="17"/>
-      <c r="W79" s="17"/>
-      <c r="X79" s="17"/>
-      <c r="Y79" s="17"/>
-      <c r="Z79" s="17"/>
-      <c r="AA79" s="17"/>
-      <c r="AB79" s="17"/>
-      <c r="AC79" s="18"/>
+      <c r="E79" s="16"/>
+      <c r="F79" s="16"/>
+      <c r="G79" s="16"/>
+      <c r="H79" s="16"/>
+      <c r="I79" s="16"/>
+      <c r="J79" s="16"/>
+      <c r="K79" s="16"/>
+      <c r="L79" s="16"/>
+      <c r="M79" s="16"/>
+      <c r="N79" s="16"/>
+      <c r="O79" s="16"/>
+      <c r="P79" s="16"/>
+      <c r="Q79" s="16"/>
+      <c r="R79" s="16"/>
+      <c r="S79" s="16"/>
+      <c r="T79" s="16"/>
+      <c r="U79" s="16"/>
+      <c r="V79" s="16"/>
+      <c r="W79" s="16"/>
+      <c r="X79" s="16"/>
+      <c r="Y79" s="16"/>
+      <c r="Z79" s="16"/>
+      <c r="AA79" s="16"/>
+      <c r="AB79" s="16"/>
+      <c r="AC79" s="17"/>
     </row>
     <row r="81" spans="3:32" x14ac:dyDescent="0.4">
-      <c r="C81" s="8" t="s">
+      <c r="C81" s="7" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="82" spans="3:32" x14ac:dyDescent="0.4">
-      <c r="D82" s="19" t="s">
+      <c r="D82" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="E82" s="20"/>
-      <c r="F82" s="20"/>
-      <c r="G82" s="20"/>
-      <c r="H82" s="20"/>
-      <c r="I82" s="20"/>
-      <c r="J82" s="20"/>
-      <c r="K82" s="20"/>
-      <c r="L82" s="20"/>
-      <c r="M82" s="20"/>
-      <c r="N82" s="20"/>
-      <c r="O82" s="20"/>
-      <c r="P82" s="20"/>
-      <c r="Q82" s="20"/>
-      <c r="R82" s="20"/>
-      <c r="S82" s="20"/>
-      <c r="T82" s="20"/>
-      <c r="U82" s="20"/>
-      <c r="V82" s="20"/>
-      <c r="W82" s="20"/>
-      <c r="X82" s="20"/>
-      <c r="Y82" s="20"/>
-      <c r="Z82" s="20"/>
-      <c r="AA82" s="20"/>
-      <c r="AB82" s="20"/>
-      <c r="AC82" s="20"/>
-      <c r="AD82" s="20"/>
-      <c r="AE82" s="20"/>
-      <c r="AF82" s="21"/>
+      <c r="E82" s="19"/>
+      <c r="F82" s="19"/>
+      <c r="G82" s="19"/>
+      <c r="H82" s="19"/>
+      <c r="I82" s="19"/>
+      <c r="J82" s="19"/>
+      <c r="K82" s="19"/>
+      <c r="L82" s="19"/>
+      <c r="M82" s="19"/>
+      <c r="N82" s="19"/>
+      <c r="O82" s="19"/>
+      <c r="P82" s="19"/>
+      <c r="Q82" s="19"/>
+      <c r="R82" s="19"/>
+      <c r="S82" s="19"/>
+      <c r="T82" s="19"/>
+      <c r="U82" s="19"/>
+      <c r="V82" s="19"/>
+      <c r="W82" s="19"/>
+      <c r="X82" s="19"/>
+      <c r="Y82" s="19"/>
+      <c r="Z82" s="19"/>
+      <c r="AA82" s="19"/>
+      <c r="AB82" s="19"/>
+      <c r="AC82" s="19"/>
+      <c r="AD82" s="19"/>
+      <c r="AE82" s="19"/>
+      <c r="AF82" s="20"/>
     </row>
     <row r="84" spans="3:32" x14ac:dyDescent="0.4">
-      <c r="C84" s="8" t="s">
+      <c r="C84" s="7" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="85" spans="3:32" x14ac:dyDescent="0.4">
-      <c r="D85" s="19" t="s">
+      <c r="D85" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="E85" s="20"/>
-      <c r="F85" s="20"/>
-      <c r="G85" s="20"/>
-      <c r="H85" s="20"/>
-      <c r="I85" s="20"/>
-      <c r="J85" s="20"/>
-      <c r="K85" s="20"/>
-      <c r="L85" s="20"/>
-      <c r="M85" s="20"/>
-      <c r="N85" s="20"/>
-      <c r="O85" s="20"/>
-      <c r="P85" s="20"/>
-      <c r="Q85" s="20"/>
-      <c r="R85" s="20"/>
-      <c r="S85" s="20"/>
-      <c r="T85" s="20"/>
-      <c r="U85" s="20"/>
-      <c r="V85" s="20"/>
-      <c r="W85" s="20"/>
-      <c r="X85" s="20"/>
-      <c r="Y85" s="20"/>
-      <c r="Z85" s="20"/>
-      <c r="AA85" s="20"/>
-      <c r="AB85" s="20"/>
-      <c r="AC85" s="20"/>
-      <c r="AD85" s="20"/>
-      <c r="AE85" s="20"/>
-      <c r="AF85" s="21"/>
+      <c r="E85" s="19"/>
+      <c r="F85" s="19"/>
+      <c r="G85" s="19"/>
+      <c r="H85" s="19"/>
+      <c r="I85" s="19"/>
+      <c r="J85" s="19"/>
+      <c r="K85" s="19"/>
+      <c r="L85" s="19"/>
+      <c r="M85" s="19"/>
+      <c r="N85" s="19"/>
+      <c r="O85" s="19"/>
+      <c r="P85" s="19"/>
+      <c r="Q85" s="19"/>
+      <c r="R85" s="19"/>
+      <c r="S85" s="19"/>
+      <c r="T85" s="19"/>
+      <c r="U85" s="19"/>
+      <c r="V85" s="19"/>
+      <c r="W85" s="19"/>
+      <c r="X85" s="19"/>
+      <c r="Y85" s="19"/>
+      <c r="Z85" s="19"/>
+      <c r="AA85" s="19"/>
+      <c r="AB85" s="19"/>
+      <c r="AC85" s="19"/>
+      <c r="AD85" s="19"/>
+      <c r="AE85" s="19"/>
+      <c r="AF85" s="20"/>
     </row>
     <row r="87" spans="3:32" x14ac:dyDescent="0.4">
-      <c r="D87" s="8" t="s">
+      <c r="D87" s="7" t="s">
         <v>60</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="AN28:AQ28"/>
-    <mergeCell ref="AN22:AQ22"/>
-    <mergeCell ref="AN23:AQ23"/>
-    <mergeCell ref="AN24:AQ24"/>
-    <mergeCell ref="AN25:AQ25"/>
-    <mergeCell ref="AN26:AQ26"/>
-    <mergeCell ref="AN27:AQ27"/>
-    <mergeCell ref="AJ23:AM23"/>
-    <mergeCell ref="AJ24:AM24"/>
-    <mergeCell ref="AJ25:AM25"/>
-    <mergeCell ref="AJ26:AM26"/>
-    <mergeCell ref="AJ27:AM27"/>
     <mergeCell ref="AJ28:AM28"/>
     <mergeCell ref="AJ22:AM22"/>
     <mergeCell ref="AF22:AI22"/>
@@ -3197,6 +3454,18 @@
     <mergeCell ref="AF26:AI26"/>
     <mergeCell ref="AF27:AI27"/>
     <mergeCell ref="AF28:AI28"/>
+    <mergeCell ref="AJ23:AM23"/>
+    <mergeCell ref="AJ24:AM24"/>
+    <mergeCell ref="AJ25:AM25"/>
+    <mergeCell ref="AJ26:AM26"/>
+    <mergeCell ref="AJ27:AM27"/>
+    <mergeCell ref="AN28:AQ28"/>
+    <mergeCell ref="AN22:AQ22"/>
+    <mergeCell ref="AN23:AQ23"/>
+    <mergeCell ref="AN24:AQ24"/>
+    <mergeCell ref="AN25:AQ25"/>
+    <mergeCell ref="AN26:AQ26"/>
+    <mergeCell ref="AN27:AQ27"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <hyperlinks>
@@ -3204,4 +3473,459 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1F0D740-3B62-423E-AB9D-226091A850A3}">
+  <dimension ref="B2:K8"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="2" max="2" width="5.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="3.625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="30.625" style="50" customWidth="1"/>
+    <col min="6" max="6" width="3.625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="30.625" style="50" customWidth="1"/>
+    <col min="8" max="8" width="3.625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="30.625" style="50" customWidth="1"/>
+    <col min="10" max="10" width="3.625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="30.625" style="50" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="43" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="44" t="s">
+        <v>96</v>
+      </c>
+      <c r="I2" s="44"/>
+      <c r="J2" s="44"/>
+      <c r="K2" s="44"/>
+    </row>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="43"/>
+      <c r="H3" s="44" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="44"/>
+      <c r="J3" s="51" t="s">
+        <v>5</v>
+      </c>
+      <c r="K3" s="52"/>
+    </row>
+    <row r="4" spans="2:11" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="B4" s="41" t="s">
+        <v>86</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D4" s="47" t="s">
+        <v>81</v>
+      </c>
+      <c r="E4" s="49" t="s">
+        <v>99</v>
+      </c>
+      <c r="F4" s="47" t="s">
+        <v>81</v>
+      </c>
+      <c r="G4" s="48" t="s">
+        <v>97</v>
+      </c>
+      <c r="H4" s="47" t="s">
+        <v>81</v>
+      </c>
+      <c r="I4" s="48" t="s">
+        <v>97</v>
+      </c>
+      <c r="J4" s="47" t="s">
+        <v>81</v>
+      </c>
+      <c r="K4" s="48" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" ht="56.25" x14ac:dyDescent="0.4">
+      <c r="B5" s="41"/>
+      <c r="C5" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D5" s="47" t="s">
+        <v>94</v>
+      </c>
+      <c r="E5" s="49" t="s">
+        <v>98</v>
+      </c>
+      <c r="F5" s="47" t="s">
+        <v>81</v>
+      </c>
+      <c r="G5" s="48" t="s">
+        <v>97</v>
+      </c>
+      <c r="H5" s="47" t="s">
+        <v>93</v>
+      </c>
+      <c r="I5" s="48"/>
+      <c r="J5" s="47" t="s">
+        <v>81</v>
+      </c>
+      <c r="K5" s="48" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B6" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D6" s="47" t="s">
+        <v>93</v>
+      </c>
+      <c r="E6" s="48"/>
+      <c r="F6" s="47" t="s">
+        <v>81</v>
+      </c>
+      <c r="G6" s="48"/>
+      <c r="H6" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="I6" s="46"/>
+      <c r="J6" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="K6" s="46"/>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B7" s="41"/>
+      <c r="C7" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D7" s="47" t="s">
+        <v>93</v>
+      </c>
+      <c r="E7" s="48"/>
+      <c r="F7" s="47" t="s">
+        <v>93</v>
+      </c>
+      <c r="G7" s="48"/>
+      <c r="H7" s="47" t="s">
+        <v>93</v>
+      </c>
+      <c r="I7" s="48"/>
+      <c r="J7" s="47" t="s">
+        <v>93</v>
+      </c>
+      <c r="K7" s="48"/>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B8" s="41"/>
+      <c r="C8" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D8" s="47" t="s">
+        <v>93</v>
+      </c>
+      <c r="E8" s="48"/>
+      <c r="F8" s="47" t="s">
+        <v>81</v>
+      </c>
+      <c r="G8" s="48"/>
+      <c r="H8" s="47" t="s">
+        <v>93</v>
+      </c>
+      <c r="I8" s="48"/>
+      <c r="J8" s="47" t="s">
+        <v>93</v>
+      </c>
+      <c r="K8" s="48"/>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="D2:G2"/>
+    <mergeCell ref="H2:K2"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="B2:C3"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="H6:I6"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC28E947-F204-41B5-8C57-73B4C4CE2740}">
+  <dimension ref="B2:K20"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="2" max="2" width="5.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="3.625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="30.625" style="50" customWidth="1"/>
+    <col min="6" max="6" width="3.625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="30.625" style="50" customWidth="1"/>
+    <col min="8" max="8" width="3.625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="30.625" style="50" customWidth="1"/>
+    <col min="10" max="10" width="3.625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="30.625" style="50" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="43" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="44" t="s">
+        <v>96</v>
+      </c>
+      <c r="I2" s="44"/>
+      <c r="J2" s="44"/>
+      <c r="K2" s="44"/>
+    </row>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="43"/>
+      <c r="H3" s="44" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="44"/>
+      <c r="J3" s="51" t="s">
+        <v>5</v>
+      </c>
+      <c r="K3" s="52"/>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B4" s="41" t="s">
+        <v>86</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="D4" s="53" t="s">
+        <v>81</v>
+      </c>
+      <c r="E4" s="54" t="s">
+        <v>100</v>
+      </c>
+      <c r="F4" s="53" t="s">
+        <v>81</v>
+      </c>
+      <c r="G4" s="55" t="s">
+        <v>109</v>
+      </c>
+      <c r="H4" s="53" t="s">
+        <v>81</v>
+      </c>
+      <c r="I4" s="55" t="s">
+        <v>102</v>
+      </c>
+      <c r="J4" s="53" t="s">
+        <v>81</v>
+      </c>
+      <c r="K4" s="55" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B5" s="41"/>
+      <c r="C5" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D5" s="56" t="s">
+        <v>94</v>
+      </c>
+      <c r="E5" s="57" t="s">
+        <v>101</v>
+      </c>
+      <c r="F5" s="53" t="s">
+        <v>81</v>
+      </c>
+      <c r="G5" s="55" t="s">
+        <v>110</v>
+      </c>
+      <c r="H5" s="56" t="s">
+        <v>93</v>
+      </c>
+      <c r="I5" s="57" t="s">
+        <v>103</v>
+      </c>
+      <c r="J5" s="53" t="s">
+        <v>81</v>
+      </c>
+      <c r="K5" s="55" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B6" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="D6" s="56" t="s">
+        <v>93</v>
+      </c>
+      <c r="E6" s="58" t="s">
+        <v>101</v>
+      </c>
+      <c r="F6" s="53" t="s">
+        <v>81</v>
+      </c>
+      <c r="G6" s="55" t="s">
+        <v>110</v>
+      </c>
+      <c r="H6" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="I6" s="46"/>
+      <c r="J6" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="K6" s="46"/>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B7" s="41"/>
+      <c r="C7" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="D7" s="56" t="s">
+        <v>93</v>
+      </c>
+      <c r="E7" s="58" t="s">
+        <v>101</v>
+      </c>
+      <c r="F7" s="56" t="s">
+        <v>93</v>
+      </c>
+      <c r="G7" s="58" t="s">
+        <v>110</v>
+      </c>
+      <c r="H7" s="56" t="s">
+        <v>93</v>
+      </c>
+      <c r="I7" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="J7" s="56" t="s">
+        <v>93</v>
+      </c>
+      <c r="K7" s="58" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B8" s="41"/>
+      <c r="C8" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D8" s="56" t="s">
+        <v>93</v>
+      </c>
+      <c r="E8" s="58" t="s">
+        <v>101</v>
+      </c>
+      <c r="F8" s="53" t="s">
+        <v>81</v>
+      </c>
+      <c r="G8" s="55" t="s">
+        <v>110</v>
+      </c>
+      <c r="H8" s="56" t="s">
+        <v>93</v>
+      </c>
+      <c r="I8" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="J8" s="56" t="s">
+        <v>93</v>
+      </c>
+      <c r="K8" s="58" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B13" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B14" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B15" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B18" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B19" t="s">
+        <v>106</v>
+      </c>
+      <c r="C19" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B20" t="s">
+        <v>107</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="B2:C3"/>
+    <mergeCell ref="D2:G2"/>
+    <mergeCell ref="H2:K2"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:K3"/>
+  </mergeCells>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/調査内容/アウトプット.xlsx
+++ b/調査内容/アウトプット.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\aaa\elkstack\調査内容\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A945A13E-6CD5-4D91-99D8-64C1BC2853FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C811044-B071-4A6E-8B21-6119AB383405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{FE37317B-BE23-49EA-9156-A5F997289FA1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{FE37317B-BE23-49EA-9156-A5F997289FA1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,8 @@
     <sheet name="GmailでSMTP送信する設定 (2)" sheetId="6" r:id="rId4"/>
     <sheet name="Sheet2" sheetId="7" r:id="rId5"/>
     <sheet name="Sheet2 (2)" sheetId="8" r:id="rId6"/>
+    <sheet name="調査結果" sheetId="9" r:id="rId7"/>
+    <sheet name="所感" sheetId="10" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="142">
   <si>
     <t>徐々に上昇、減少する値が一定値を超えたら</t>
     <rPh sb="0" eb="2">
@@ -411,39 +413,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>異常検知_振動_機械学習_徐々に変化</t>
-    <rPh sb="16" eb="18">
-      <t>ヘンカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>異常検知_振動_機械学習_急激に変化</t>
-    <rPh sb="13" eb="15">
-      <t>キュウゲキ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>ヘンカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>異常検知_振動_機械学習_徐々に変化_pmup-01のみ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>異常検知_振動_機械学習_徐々に変化_motor-01のみ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>異常検知_振動_機械学習_急激に変化_pmup-01のみ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>異常検知_振動_機械学習_急激に変化_motor-01のみ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>GmailでSMTP送信する設定</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -944,6 +913,322 @@
   </si>
   <si>
     <t>異常スコア &gt;= 75</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>予兆検知_振動_固定閾値</t>
+    <rPh sb="0" eb="2">
+      <t>ヨチョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>異常検知_振動_固定閾値</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>異常検知_振動_機械学習</t>
+    <rPh sb="8" eb="12">
+      <t>キカイガクシュウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>予兆検知_振動_機械学習</t>
+    <rPh sb="0" eb="2">
+      <t>ヨチョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>異常検知_振動_機械学習</t>
+    <rPh sb="5" eb="7">
+      <t>シンドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アラート抑止</t>
+    <rPh sb="4" eb="6">
+      <t>ヨクシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>高頻度で出力されるデータ</t>
+    <rPh sb="0" eb="3">
+      <t>コウヒンド</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>シュツリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>低頻度で出力されるデータ</t>
+    <rPh sb="0" eb="3">
+      <t>テイヒンド</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>シュツリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>正常 ⇒ 異常</t>
+    <rPh sb="0" eb="2">
+      <t>セイジョウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>イジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>異常 ⇒ 異常</t>
+    <rPh sb="5" eb="7">
+      <t>イジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スパイクが発生しない</t>
+    <rPh sb="5" eb="7">
+      <t>ハッセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スパイクが少ない</t>
+    <rPh sb="5" eb="6">
+      <t>スク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スパイクが多い</t>
+    <rPh sb="5" eb="6">
+      <t>オオ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データのタイプ別に、望ましいと考えられる設定方法を記載</t>
+    <rPh sb="7" eb="8">
+      <t>ベツ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ノゾ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>カンガ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ホウホウ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>キサイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>データのタイプ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>状態の変化</t>
+    <rPh sb="0" eb="2">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ヘンカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1. データ毎に考えられるアラート設定</t>
+    <rPh sb="6" eb="7">
+      <t>ゴト</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>カンガ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>連続条件一致で検知</t>
+    <rPh sb="7" eb="9">
+      <t>ケンチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1. 前提</t>
+    <rPh sb="3" eb="5">
+      <t>ゼンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>どのようなデータに対してアラート検知をするか。</t>
+    <rPh sb="9" eb="10">
+      <t>タイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ケンチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1. スケジュールとループバック時間の設定</t>
+    <rPh sb="16" eb="18">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>セッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2. グループ化</t>
+    <rPh sb="7" eb="8">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3. 状態変化通知</t>
+    <rPh sb="3" eb="5">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ヘンカ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ツウチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>期間集計した結果で検知</t>
+    <rPh sb="0" eb="2">
+      <t>キカン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シュウケイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ケッカ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ケンチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>中央値</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>平均値</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最高値</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最低値</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（設定方法）</t>
+    <rPh sb="1" eb="3">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ホウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（動作イメージ）</t>
+    <rPh sb="1" eb="3">
+      <t>ドウサ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>継続通知</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>状態変化通知</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4. アラート重複排除・抑制</t>
+    <rPh sb="7" eb="9">
+      <t>ジュウフク</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ハイジョ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ヨクセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1. アラート制御方法</t>
+    <rPh sb="7" eb="9">
+      <t>セイギョ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ホウホウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>複数件で判定</t>
+    <rPh sb="0" eb="2">
+      <t>フクスウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ケン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>条件一致で検知</t>
+    <rPh sb="0" eb="2">
+      <t>ジョウケン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>イッチ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ケンチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2. 検知条件</t>
+    <rPh sb="3" eb="5">
+      <t>ケンチ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ジョウケン</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -951,7 +1236,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1001,6 +1286,31 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -1039,7 +1349,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -1214,8 +1524,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1228,8 +1547,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1341,6 +1663,60 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1354,62 +1730,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="4" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="2" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="5">
     <cellStyle name="ハイパーリンク" xfId="3" builtinId="8"/>
+    <cellStyle name="見出し 1" xfId="4" builtinId="16"/>
     <cellStyle name="見出し 2" xfId="1" builtinId="17"/>
     <cellStyle name="見出し 3" xfId="2" builtinId="18"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -2232,38 +2564,38 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:15" x14ac:dyDescent="0.4">
-      <c r="D3" s="42" t="s">
+      <c r="D3" s="54" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="42"/>
-      <c r="J3" s="42"/>
-      <c r="K3" s="42"/>
-      <c r="L3" s="42"/>
-      <c r="M3" s="42"/>
-      <c r="N3" s="42"/>
-      <c r="O3" s="42"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="54"/>
+      <c r="J3" s="54"/>
+      <c r="K3" s="54"/>
+      <c r="L3" s="54"/>
+      <c r="M3" s="54"/>
+      <c r="N3" s="54"/>
+      <c r="O3" s="54"/>
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.4">
-      <c r="D4" s="41" t="s">
+      <c r="D4" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="47"/>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.4">
       <c r="D5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="41" t="s">
+      <c r="E5" s="47" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
+      <c r="F5" s="47"/>
+      <c r="G5" s="47"/>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.4">
       <c r="D6" s="3" t="s">
@@ -2316,70 +2648,58 @@
         <v>22</v>
       </c>
       <c r="C9" t="s">
-        <v>0</v>
-      </c>
-      <c r="D9" s="41" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>38</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="D9" s="59" t="s">
+        <v>106</v>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="F9" s="59" t="s">
+        <v>107</v>
+      </c>
+      <c r="G9" s="4"/>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.4">
       <c r="C10" t="s">
-        <v>1</v>
-      </c>
-      <c r="D10" s="41"/>
-      <c r="E10" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>40</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="D10" s="59" t="s">
+        <v>105</v>
+      </c>
+      <c r="E10" s="4"/>
+      <c r="F10" s="59" t="s">
+        <v>108</v>
+      </c>
+      <c r="G10" s="4"/>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.4">
       <c r="B11" t="s">
         <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>0</v>
-      </c>
-      <c r="D11" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>38</v>
-      </c>
+      <c r="E11" s="4"/>
+      <c r="F11" s="59" t="s">
+        <v>109</v>
+      </c>
+      <c r="G11" s="4"/>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.4">
       <c r="C12" t="s">
-        <v>1</v>
-      </c>
-      <c r="D12" s="41"/>
-      <c r="E12" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>40</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="D12" s="59" t="s">
+        <v>105</v>
+      </c>
+      <c r="E12" s="4"/>
+      <c r="F12" s="59" t="s">
+        <v>108</v>
+      </c>
+      <c r="G12" s="4"/>
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.4">
       <c r="D13" s="4"/>
@@ -2472,12 +2792,10 @@
       <c r="G27" s="4"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="3">
     <mergeCell ref="E5:G5"/>
-    <mergeCell ref="D9:D10"/>
     <mergeCell ref="D4:G4"/>
     <mergeCell ref="D3:O3"/>
-    <mergeCell ref="D11:D12"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2494,58 +2812,58 @@
   <sheetData>
     <row r="1" spans="1:5" ht="21" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="6" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="16.5" thickTop="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="1:5" ht="18.75" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B3" s="8" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.4">
       <c r="C4" s="7" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.4">
       <c r="D5" s="7" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18.75" x14ac:dyDescent="0.4">
       <c r="E6" s="9" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.4">
       <c r="D8" s="7" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="28" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C28" s="7" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="48" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C48" s="7" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="73" spans="2:30" ht="18.75" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B73" s="8" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="74" spans="2:30" x14ac:dyDescent="0.4">
       <c r="C74" s="7" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="75" spans="2:30" x14ac:dyDescent="0.4">
       <c r="D75" s="10" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E75" s="11"/>
       <c r="F75" s="11"/>
@@ -2575,22 +2893,22 @@
     </row>
     <row r="76" spans="2:30" x14ac:dyDescent="0.4">
       <c r="D76" s="13" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="AC76" s="14"/>
     </row>
     <row r="77" spans="2:30" x14ac:dyDescent="0.4">
       <c r="D77" s="13" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="AC77" s="14"/>
       <c r="AD77" s="7" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="78" spans="2:30" x14ac:dyDescent="0.4">
       <c r="D78" s="15" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E78" s="16"/>
       <c r="F78" s="16"/>
@@ -2620,12 +2938,12 @@
     </row>
     <row r="80" spans="2:30" x14ac:dyDescent="0.4">
       <c r="C80" s="7" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="81" spans="3:32" x14ac:dyDescent="0.4">
       <c r="D81" s="18" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E81" s="19"/>
       <c r="F81" s="19"/>
@@ -2658,12 +2976,12 @@
     </row>
     <row r="83" spans="3:32" x14ac:dyDescent="0.4">
       <c r="C83" s="7" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="84" spans="3:32" x14ac:dyDescent="0.4">
       <c r="D84" s="18" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E84" s="19"/>
       <c r="F84" s="19"/>
@@ -2696,7 +3014,7 @@
     </row>
     <row r="86" spans="3:32" x14ac:dyDescent="0.4">
       <c r="D86" s="7" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -2719,46 +3037,46 @@
   <sheetData>
     <row r="1" spans="1:55" ht="21" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="6" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:55" ht="16.5" thickTop="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="1:55" ht="18.75" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B3" s="8" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:55" x14ac:dyDescent="0.4">
       <c r="C4" s="7" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:55" x14ac:dyDescent="0.4">
       <c r="D5" s="7" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:55" ht="18.75" x14ac:dyDescent="0.4">
       <c r="E6" s="9" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:55" ht="18.75" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B10" s="8" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="BC10" s="21"/>
     </row>
     <row r="15" spans="1:55" ht="18.75" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B15" s="8" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17" spans="3:43" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="18" spans="3:43" ht="15.75" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="19" spans="3:43" x14ac:dyDescent="0.4">
       <c r="C19" s="22" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D19" s="23"/>
       <c r="E19" s="23"/>
@@ -2774,7 +3092,7 @@
       <c r="O19" s="23"/>
       <c r="P19" s="24"/>
       <c r="Q19" s="22" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="R19" s="23"/>
       <c r="S19" s="23"/>
@@ -2791,7 +3109,7 @@
       <c r="AD19" s="23"/>
       <c r="AE19" s="24"/>
       <c r="AF19" s="25" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AG19" s="26"/>
       <c r="AH19" s="26"/>
@@ -2836,19 +3154,19 @@
       <c r="AD20" s="29"/>
       <c r="AE20" s="30"/>
       <c r="AF20" s="22" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="AG20" s="23"/>
       <c r="AH20" s="23"/>
       <c r="AI20" s="24"/>
       <c r="AJ20" s="22" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="AK20" s="23"/>
       <c r="AL20" s="23"/>
       <c r="AM20" s="24"/>
       <c r="AN20" s="22" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="AO20" s="23"/>
       <c r="AP20" s="23"/>
@@ -2889,13 +3207,13 @@
       <c r="AH21" s="35"/>
       <c r="AI21" s="36"/>
       <c r="AJ21" s="34" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="AK21" s="35"/>
       <c r="AL21" s="35"/>
       <c r="AM21" s="33"/>
       <c r="AN21" s="34" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="AO21" s="35"/>
       <c r="AP21" s="35"/>
@@ -2903,7 +3221,7 @@
     </row>
     <row r="22" spans="3:43" x14ac:dyDescent="0.4">
       <c r="C22" s="18" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D22" s="19"/>
       <c r="E22" s="19"/>
@@ -2919,7 +3237,7 @@
       <c r="O22" s="19"/>
       <c r="P22" s="20"/>
       <c r="Q22" s="18" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="R22" s="19"/>
       <c r="S22" s="19"/>
@@ -2935,28 +3253,28 @@
       <c r="AC22" s="19"/>
       <c r="AD22" s="19"/>
       <c r="AE22" s="20"/>
-      <c r="AF22" s="38" t="s">
-        <v>81</v>
-      </c>
-      <c r="AG22" s="39"/>
-      <c r="AH22" s="39"/>
-      <c r="AI22" s="40"/>
-      <c r="AJ22" s="37" t="s">
-        <v>81</v>
-      </c>
-      <c r="AK22" s="37"/>
-      <c r="AL22" s="37"/>
-      <c r="AM22" s="37"/>
-      <c r="AN22" s="37" t="s">
-        <v>81</v>
-      </c>
-      <c r="AO22" s="37"/>
-      <c r="AP22" s="37"/>
-      <c r="AQ22" s="37"/>
+      <c r="AF22" s="56" t="s">
+        <v>75</v>
+      </c>
+      <c r="AG22" s="57"/>
+      <c r="AH22" s="57"/>
+      <c r="AI22" s="58"/>
+      <c r="AJ22" s="55" t="s">
+        <v>75</v>
+      </c>
+      <c r="AK22" s="55"/>
+      <c r="AL22" s="55"/>
+      <c r="AM22" s="55"/>
+      <c r="AN22" s="55" t="s">
+        <v>75</v>
+      </c>
+      <c r="AO22" s="55"/>
+      <c r="AP22" s="55"/>
+      <c r="AQ22" s="55"/>
     </row>
     <row r="23" spans="3:43" x14ac:dyDescent="0.4">
       <c r="C23" s="18" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D23" s="19"/>
       <c r="E23" s="19"/>
@@ -2972,7 +3290,7 @@
       <c r="O23" s="19"/>
       <c r="P23" s="20"/>
       <c r="Q23" s="18" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="R23" s="19"/>
       <c r="S23" s="19"/>
@@ -2988,28 +3306,28 @@
       <c r="AC23" s="19"/>
       <c r="AD23" s="19"/>
       <c r="AE23" s="20"/>
-      <c r="AF23" s="38" t="s">
-        <v>82</v>
-      </c>
-      <c r="AG23" s="39"/>
-      <c r="AH23" s="39"/>
-      <c r="AI23" s="40"/>
-      <c r="AJ23" s="37" t="s">
-        <v>81</v>
-      </c>
-      <c r="AK23" s="37"/>
-      <c r="AL23" s="37"/>
-      <c r="AM23" s="37"/>
-      <c r="AN23" s="37" t="s">
-        <v>81</v>
-      </c>
-      <c r="AO23" s="37"/>
-      <c r="AP23" s="37"/>
-      <c r="AQ23" s="37"/>
+      <c r="AF23" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG23" s="57"/>
+      <c r="AH23" s="57"/>
+      <c r="AI23" s="58"/>
+      <c r="AJ23" s="55" t="s">
+        <v>75</v>
+      </c>
+      <c r="AK23" s="55"/>
+      <c r="AL23" s="55"/>
+      <c r="AM23" s="55"/>
+      <c r="AN23" s="55" t="s">
+        <v>75</v>
+      </c>
+      <c r="AO23" s="55"/>
+      <c r="AP23" s="55"/>
+      <c r="AQ23" s="55"/>
     </row>
     <row r="24" spans="3:43" x14ac:dyDescent="0.4">
       <c r="C24" s="18" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D24" s="19"/>
       <c r="E24" s="19"/>
@@ -3025,7 +3343,7 @@
       <c r="O24" s="19"/>
       <c r="P24" s="20"/>
       <c r="Q24" s="18" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="R24" s="19"/>
       <c r="S24" s="19"/>
@@ -3041,28 +3359,28 @@
       <c r="AC24" s="19"/>
       <c r="AD24" s="19"/>
       <c r="AE24" s="20"/>
-      <c r="AF24" s="38" t="s">
-        <v>82</v>
-      </c>
-      <c r="AG24" s="39"/>
-      <c r="AH24" s="39"/>
-      <c r="AI24" s="40"/>
-      <c r="AJ24" s="37" t="s">
-        <v>81</v>
-      </c>
-      <c r="AK24" s="37"/>
-      <c r="AL24" s="37"/>
-      <c r="AM24" s="37"/>
-      <c r="AN24" s="37" t="s">
-        <v>81</v>
-      </c>
-      <c r="AO24" s="37"/>
-      <c r="AP24" s="37"/>
-      <c r="AQ24" s="37"/>
+      <c r="AF24" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG24" s="57"/>
+      <c r="AH24" s="57"/>
+      <c r="AI24" s="58"/>
+      <c r="AJ24" s="55" t="s">
+        <v>75</v>
+      </c>
+      <c r="AK24" s="55"/>
+      <c r="AL24" s="55"/>
+      <c r="AM24" s="55"/>
+      <c r="AN24" s="55" t="s">
+        <v>75</v>
+      </c>
+      <c r="AO24" s="55"/>
+      <c r="AP24" s="55"/>
+      <c r="AQ24" s="55"/>
     </row>
     <row r="25" spans="3:43" x14ac:dyDescent="0.4">
       <c r="C25" s="18" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D25" s="19"/>
       <c r="E25" s="19"/>
@@ -3078,7 +3396,7 @@
       <c r="O25" s="19"/>
       <c r="P25" s="20"/>
       <c r="Q25" s="18" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="R25" s="19"/>
       <c r="S25" s="19"/>
@@ -3094,28 +3412,28 @@
       <c r="AC25" s="19"/>
       <c r="AD25" s="19"/>
       <c r="AE25" s="20"/>
-      <c r="AF25" s="38" t="s">
-        <v>82</v>
-      </c>
-      <c r="AG25" s="39"/>
-      <c r="AH25" s="39"/>
-      <c r="AI25" s="40"/>
-      <c r="AJ25" s="37" t="s">
-        <v>81</v>
-      </c>
-      <c r="AK25" s="37"/>
-      <c r="AL25" s="37"/>
-      <c r="AM25" s="37"/>
-      <c r="AN25" s="37" t="s">
-        <v>81</v>
-      </c>
-      <c r="AO25" s="37"/>
-      <c r="AP25" s="37"/>
-      <c r="AQ25" s="37"/>
+      <c r="AF25" s="56" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG25" s="57"/>
+      <c r="AH25" s="57"/>
+      <c r="AI25" s="58"/>
+      <c r="AJ25" s="55" t="s">
+        <v>75</v>
+      </c>
+      <c r="AK25" s="55"/>
+      <c r="AL25" s="55"/>
+      <c r="AM25" s="55"/>
+      <c r="AN25" s="55" t="s">
+        <v>75</v>
+      </c>
+      <c r="AO25" s="55"/>
+      <c r="AP25" s="55"/>
+      <c r="AQ25" s="55"/>
     </row>
     <row r="26" spans="3:43" x14ac:dyDescent="0.4">
       <c r="C26" s="18" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D26" s="19"/>
       <c r="E26" s="19"/>
@@ -3131,7 +3449,7 @@
       <c r="O26" s="19"/>
       <c r="P26" s="20"/>
       <c r="Q26" s="18" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="R26" s="19"/>
       <c r="S26" s="19"/>
@@ -3147,28 +3465,28 @@
       <c r="AC26" s="19"/>
       <c r="AD26" s="19"/>
       <c r="AE26" s="20"/>
-      <c r="AF26" s="37" t="s">
-        <v>81</v>
-      </c>
-      <c r="AG26" s="37"/>
-      <c r="AH26" s="37"/>
-      <c r="AI26" s="37"/>
-      <c r="AJ26" s="37" t="s">
-        <v>81</v>
-      </c>
-      <c r="AK26" s="37"/>
-      <c r="AL26" s="37"/>
-      <c r="AM26" s="37"/>
-      <c r="AN26" s="37" t="s">
-        <v>81</v>
-      </c>
-      <c r="AO26" s="37"/>
-      <c r="AP26" s="37"/>
-      <c r="AQ26" s="37"/>
+      <c r="AF26" s="55" t="s">
+        <v>75</v>
+      </c>
+      <c r="AG26" s="55"/>
+      <c r="AH26" s="55"/>
+      <c r="AI26" s="55"/>
+      <c r="AJ26" s="55" t="s">
+        <v>75</v>
+      </c>
+      <c r="AK26" s="55"/>
+      <c r="AL26" s="55"/>
+      <c r="AM26" s="55"/>
+      <c r="AN26" s="55" t="s">
+        <v>75</v>
+      </c>
+      <c r="AO26" s="55"/>
+      <c r="AP26" s="55"/>
+      <c r="AQ26" s="55"/>
     </row>
     <row r="27" spans="3:43" x14ac:dyDescent="0.4">
       <c r="C27" s="18" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D27" s="19"/>
       <c r="E27" s="19"/>
@@ -3184,7 +3502,7 @@
       <c r="O27" s="19"/>
       <c r="P27" s="20"/>
       <c r="Q27" s="18" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="R27" s="19"/>
       <c r="S27" s="19"/>
@@ -3200,28 +3518,28 @@
       <c r="AC27" s="19"/>
       <c r="AD27" s="19"/>
       <c r="AE27" s="20"/>
-      <c r="AF27" s="37" t="s">
-        <v>81</v>
-      </c>
-      <c r="AG27" s="37"/>
-      <c r="AH27" s="37"/>
-      <c r="AI27" s="37"/>
-      <c r="AJ27" s="37" t="s">
-        <v>81</v>
-      </c>
-      <c r="AK27" s="37"/>
-      <c r="AL27" s="37"/>
-      <c r="AM27" s="37"/>
-      <c r="AN27" s="37" t="s">
-        <v>81</v>
-      </c>
-      <c r="AO27" s="37"/>
-      <c r="AP27" s="37"/>
-      <c r="AQ27" s="37"/>
+      <c r="AF27" s="55" t="s">
+        <v>75</v>
+      </c>
+      <c r="AG27" s="55"/>
+      <c r="AH27" s="55"/>
+      <c r="AI27" s="55"/>
+      <c r="AJ27" s="55" t="s">
+        <v>75</v>
+      </c>
+      <c r="AK27" s="55"/>
+      <c r="AL27" s="55"/>
+      <c r="AM27" s="55"/>
+      <c r="AN27" s="55" t="s">
+        <v>75</v>
+      </c>
+      <c r="AO27" s="55"/>
+      <c r="AP27" s="55"/>
+      <c r="AQ27" s="55"/>
     </row>
     <row r="28" spans="3:43" x14ac:dyDescent="0.4">
       <c r="C28" s="18" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D28" s="19"/>
       <c r="E28" s="19"/>
@@ -3237,7 +3555,7 @@
       <c r="O28" s="19"/>
       <c r="P28" s="20"/>
       <c r="Q28" s="18" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="R28" s="19"/>
       <c r="S28" s="19"/>
@@ -3253,43 +3571,43 @@
       <c r="AC28" s="19"/>
       <c r="AD28" s="19"/>
       <c r="AE28" s="20"/>
-      <c r="AF28" s="37" t="s">
-        <v>81</v>
-      </c>
-      <c r="AG28" s="37"/>
-      <c r="AH28" s="37"/>
-      <c r="AI28" s="37"/>
-      <c r="AJ28" s="37" t="s">
-        <v>81</v>
-      </c>
-      <c r="AK28" s="37"/>
-      <c r="AL28" s="37"/>
-      <c r="AM28" s="37"/>
-      <c r="AN28" s="37" t="s">
-        <v>81</v>
-      </c>
-      <c r="AO28" s="37"/>
-      <c r="AP28" s="37"/>
-      <c r="AQ28" s="37"/>
+      <c r="AF28" s="55" t="s">
+        <v>75</v>
+      </c>
+      <c r="AG28" s="55"/>
+      <c r="AH28" s="55"/>
+      <c r="AI28" s="55"/>
+      <c r="AJ28" s="55" t="s">
+        <v>75</v>
+      </c>
+      <c r="AK28" s="55"/>
+      <c r="AL28" s="55"/>
+      <c r="AM28" s="55"/>
+      <c r="AN28" s="55" t="s">
+        <v>75</v>
+      </c>
+      <c r="AO28" s="55"/>
+      <c r="AP28" s="55"/>
+      <c r="AQ28" s="55"/>
     </row>
     <row r="49" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C49" s="7" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="74" spans="2:30" ht="18.75" thickBot="1" x14ac:dyDescent="0.45">
       <c r="B74" s="8" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="75" spans="2:30" x14ac:dyDescent="0.4">
       <c r="C75" s="7" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="76" spans="2:30" x14ac:dyDescent="0.4">
       <c r="D76" s="10" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="E76" s="11"/>
       <c r="F76" s="11"/>
@@ -3319,22 +3637,22 @@
     </row>
     <row r="77" spans="2:30" x14ac:dyDescent="0.4">
       <c r="D77" s="13" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="AC77" s="14"/>
     </row>
     <row r="78" spans="2:30" x14ac:dyDescent="0.4">
       <c r="D78" s="13" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="AC78" s="14"/>
       <c r="AD78" s="7" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="79" spans="2:30" x14ac:dyDescent="0.4">
       <c r="D79" s="15" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E79" s="16"/>
       <c r="F79" s="16"/>
@@ -3364,12 +3682,12 @@
     </row>
     <row r="81" spans="3:32" x14ac:dyDescent="0.4">
       <c r="C81" s="7" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="82" spans="3:32" x14ac:dyDescent="0.4">
       <c r="D82" s="18" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E82" s="19"/>
       <c r="F82" s="19"/>
@@ -3402,12 +3720,12 @@
     </row>
     <row r="84" spans="3:32" x14ac:dyDescent="0.4">
       <c r="C84" s="7" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="85" spans="3:32" x14ac:dyDescent="0.4">
       <c r="D85" s="18" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E85" s="19"/>
       <c r="F85" s="19"/>
@@ -3440,11 +3758,18 @@
     </row>
     <row r="87" spans="3:32" x14ac:dyDescent="0.4">
       <c r="D87" s="7" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="AN28:AQ28"/>
+    <mergeCell ref="AN22:AQ22"/>
+    <mergeCell ref="AN23:AQ23"/>
+    <mergeCell ref="AN24:AQ24"/>
+    <mergeCell ref="AN25:AQ25"/>
+    <mergeCell ref="AN26:AQ26"/>
+    <mergeCell ref="AN27:AQ27"/>
     <mergeCell ref="AJ28:AM28"/>
     <mergeCell ref="AJ22:AM22"/>
     <mergeCell ref="AF22:AI22"/>
@@ -3459,13 +3784,6 @@
     <mergeCell ref="AJ25:AM25"/>
     <mergeCell ref="AJ26:AM26"/>
     <mergeCell ref="AJ27:AM27"/>
-    <mergeCell ref="AN28:AQ28"/>
-    <mergeCell ref="AN22:AQ22"/>
-    <mergeCell ref="AN23:AQ23"/>
-    <mergeCell ref="AN24:AQ24"/>
-    <mergeCell ref="AN25:AQ25"/>
-    <mergeCell ref="AN26:AQ26"/>
-    <mergeCell ref="AN27:AQ27"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <hyperlinks>
@@ -3483,178 +3801,178 @@
     <col min="2" max="2" width="5.25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="25.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="3.625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="30.625" style="50" customWidth="1"/>
+    <col min="5" max="5" width="30.625" style="40" customWidth="1"/>
     <col min="6" max="6" width="3.625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="30.625" style="50" customWidth="1"/>
+    <col min="7" max="7" width="30.625" style="40" customWidth="1"/>
     <col min="8" max="8" width="3.625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="30.625" style="50" customWidth="1"/>
+    <col min="9" max="9" width="30.625" style="40" customWidth="1"/>
     <col min="10" max="10" width="3.625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="30.625" style="50" customWidth="1"/>
+    <col min="11" max="11" width="30.625" style="40" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="43" t="s">
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="44" t="s">
-        <v>96</v>
-      </c>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
-      <c r="K2" s="44"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="51" t="s">
+        <v>90</v>
+      </c>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51"/>
+      <c r="K2" s="51"/>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="43" t="s">
+      <c r="B3" s="47"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="43"/>
-      <c r="F3" s="43" t="s">
+      <c r="E3" s="50"/>
+      <c r="F3" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="43"/>
-      <c r="H3" s="44" t="s">
+      <c r="G3" s="50"/>
+      <c r="H3" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="44"/>
-      <c r="J3" s="51" t="s">
+      <c r="I3" s="51"/>
+      <c r="J3" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="52"/>
+      <c r="K3" s="53"/>
     </row>
     <row r="4" spans="2:11" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="B4" s="41" t="s">
+      <c r="B4" s="47" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D4" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="E4" s="39" t="s">
+        <v>93</v>
+      </c>
+      <c r="F4" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="G4" s="38" t="s">
+        <v>91</v>
+      </c>
+      <c r="H4" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="I4" s="38" t="s">
+        <v>91</v>
+      </c>
+      <c r="J4" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="K4" s="38" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" ht="56.25" x14ac:dyDescent="0.4">
+      <c r="B5" s="47"/>
+      <c r="C5" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D5" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="E5" s="39" t="s">
+        <v>92</v>
+      </c>
+      <c r="F5" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="G5" s="38" t="s">
         <v>91</v>
       </c>
-      <c r="D4" s="47" t="s">
+      <c r="H5" s="37" t="s">
+        <v>87</v>
+      </c>
+      <c r="I5" s="38"/>
+      <c r="J5" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="K5" s="38" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B6" s="47" t="s">
         <v>81</v>
       </c>
-      <c r="E4" s="49" t="s">
-        <v>99</v>
-      </c>
-      <c r="F4" s="47" t="s">
-        <v>81</v>
-      </c>
-      <c r="G4" s="48" t="s">
-        <v>97</v>
-      </c>
-      <c r="H4" s="47" t="s">
-        <v>81</v>
-      </c>
-      <c r="I4" s="48" t="s">
-        <v>97</v>
-      </c>
-      <c r="J4" s="47" t="s">
-        <v>81</v>
-      </c>
-      <c r="K4" s="48" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="5" spans="2:11" ht="56.25" x14ac:dyDescent="0.4">
-      <c r="B5" s="41"/>
-      <c r="C5" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="D5" s="47" t="s">
-        <v>94</v>
-      </c>
-      <c r="E5" s="49" t="s">
-        <v>98</v>
-      </c>
-      <c r="F5" s="47" t="s">
-        <v>81</v>
-      </c>
-      <c r="G5" s="48" t="s">
-        <v>97</v>
-      </c>
-      <c r="H5" s="47" t="s">
-        <v>93</v>
-      </c>
-      <c r="I5" s="48"/>
-      <c r="J5" s="47" t="s">
-        <v>81</v>
-      </c>
-      <c r="K5" s="48" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B6" s="41" t="s">
+      <c r="C6" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D6" s="37" t="s">
         <v>87</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="D6" s="47" t="s">
-        <v>93</v>
-      </c>
-      <c r="E6" s="48"/>
-      <c r="F6" s="47" t="s">
-        <v>81</v>
-      </c>
-      <c r="G6" s="48"/>
-      <c r="H6" s="45" t="s">
-        <v>95</v>
-      </c>
-      <c r="I6" s="46"/>
-      <c r="J6" s="45" t="s">
-        <v>95</v>
-      </c>
-      <c r="K6" s="46"/>
+      <c r="E6" s="38"/>
+      <c r="F6" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="G6" s="38"/>
+      <c r="H6" s="48" t="s">
+        <v>89</v>
+      </c>
+      <c r="I6" s="49"/>
+      <c r="J6" s="48" t="s">
+        <v>89</v>
+      </c>
+      <c r="K6" s="49"/>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B7" s="41"/>
+      <c r="B7" s="47"/>
       <c r="C7" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="D7" s="47" t="s">
-        <v>93</v>
-      </c>
-      <c r="E7" s="48"/>
-      <c r="F7" s="47" t="s">
-        <v>93</v>
-      </c>
-      <c r="G7" s="48"/>
-      <c r="H7" s="47" t="s">
-        <v>93</v>
-      </c>
-      <c r="I7" s="48"/>
-      <c r="J7" s="47" t="s">
-        <v>93</v>
-      </c>
-      <c r="K7" s="48"/>
+        <v>83</v>
+      </c>
+      <c r="D7" s="37" t="s">
+        <v>87</v>
+      </c>
+      <c r="E7" s="38"/>
+      <c r="F7" s="37" t="s">
+        <v>87</v>
+      </c>
+      <c r="G7" s="38"/>
+      <c r="H7" s="37" t="s">
+        <v>87</v>
+      </c>
+      <c r="I7" s="38"/>
+      <c r="J7" s="37" t="s">
+        <v>87</v>
+      </c>
+      <c r="K7" s="38"/>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B8" s="41"/>
+      <c r="B8" s="47"/>
       <c r="C8" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D8" s="47" t="s">
-        <v>93</v>
-      </c>
-      <c r="E8" s="48"/>
-      <c r="F8" s="47" t="s">
-        <v>81</v>
-      </c>
-      <c r="G8" s="48"/>
-      <c r="H8" s="47" t="s">
-        <v>93</v>
-      </c>
-      <c r="I8" s="48"/>
-      <c r="J8" s="47" t="s">
-        <v>93</v>
-      </c>
-      <c r="K8" s="48"/>
+        <v>84</v>
+      </c>
+      <c r="D8" s="37" t="s">
+        <v>87</v>
+      </c>
+      <c r="E8" s="38"/>
+      <c r="F8" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="G8" s="38"/>
+      <c r="H8" s="37" t="s">
+        <v>87</v>
+      </c>
+      <c r="I8" s="38"/>
+      <c r="J8" s="37" t="s">
+        <v>87</v>
+      </c>
+      <c r="K8" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -3683,232 +4001,232 @@
     <col min="2" max="2" width="5.25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="25.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="3.625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="30.625" style="50" customWidth="1"/>
+    <col min="5" max="5" width="30.625" style="40" customWidth="1"/>
     <col min="6" max="6" width="3.625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="30.625" style="50" customWidth="1"/>
+    <col min="7" max="7" width="30.625" style="40" customWidth="1"/>
     <col min="8" max="8" width="3.625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="30.625" style="50" customWidth="1"/>
+    <col min="9" max="9" width="30.625" style="40" customWidth="1"/>
     <col min="10" max="10" width="3.625" style="2" customWidth="1"/>
-    <col min="11" max="11" width="30.625" style="50" customWidth="1"/>
+    <col min="11" max="11" width="30.625" style="40" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="43" t="s">
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="44" t="s">
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="51" t="s">
+        <v>90</v>
+      </c>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51"/>
+      <c r="K2" s="51"/>
+    </row>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B3" s="47"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="50" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="50"/>
+      <c r="F3" s="50" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="50"/>
+      <c r="H3" s="51" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="51"/>
+      <c r="J3" s="52" t="s">
+        <v>5</v>
+      </c>
+      <c r="K3" s="53"/>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B4" s="47" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D4" s="42" t="s">
+        <v>75</v>
+      </c>
+      <c r="E4" s="43" t="s">
+        <v>94</v>
+      </c>
+      <c r="F4" s="42" t="s">
+        <v>75</v>
+      </c>
+      <c r="G4" s="44" t="s">
+        <v>103</v>
+      </c>
+      <c r="H4" s="42" t="s">
+        <v>75</v>
+      </c>
+      <c r="I4" s="44" t="s">
         <v>96</v>
       </c>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
-      <c r="K2" s="44"/>
-    </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B3" s="41"/>
-      <c r="C3" s="41"/>
-      <c r="D3" s="43" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3" s="43"/>
-      <c r="F3" s="43" t="s">
-        <v>5</v>
-      </c>
-      <c r="G3" s="43"/>
-      <c r="H3" s="44" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" s="44"/>
-      <c r="J3" s="51" t="s">
-        <v>5</v>
-      </c>
-      <c r="K3" s="52"/>
-    </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B4" s="41" t="s">
+      <c r="J4" s="42" t="s">
+        <v>75</v>
+      </c>
+      <c r="K4" s="44" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B5" s="47"/>
+      <c r="C5" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="D4" s="53" t="s">
+      <c r="D5" s="41" t="s">
+        <v>88</v>
+      </c>
+      <c r="E5" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="F5" s="42" t="s">
+        <v>75</v>
+      </c>
+      <c r="G5" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="H5" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="I5" s="45" t="s">
+        <v>97</v>
+      </c>
+      <c r="J5" s="42" t="s">
+        <v>75</v>
+      </c>
+      <c r="K5" s="44" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B6" s="47" t="s">
         <v>81</v>
       </c>
-      <c r="E4" s="54" t="s">
-        <v>100</v>
-      </c>
-      <c r="F4" s="53" t="s">
-        <v>81</v>
-      </c>
-      <c r="G4" s="55" t="s">
-        <v>109</v>
-      </c>
-      <c r="H4" s="53" t="s">
-        <v>81</v>
-      </c>
-      <c r="I4" s="55" t="s">
-        <v>102</v>
-      </c>
-      <c r="J4" s="53" t="s">
-        <v>81</v>
-      </c>
-      <c r="K4" s="55" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B5" s="41"/>
-      <c r="C5" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="D5" s="56" t="s">
-        <v>94</v>
-      </c>
-      <c r="E5" s="57" t="s">
-        <v>101</v>
-      </c>
-      <c r="F5" s="53" t="s">
-        <v>81</v>
-      </c>
-      <c r="G5" s="55" t="s">
-        <v>110</v>
-      </c>
-      <c r="H5" s="56" t="s">
-        <v>93</v>
-      </c>
-      <c r="I5" s="57" t="s">
-        <v>103</v>
-      </c>
-      <c r="J5" s="53" t="s">
-        <v>81</v>
-      </c>
-      <c r="K5" s="55" t="s">
+      <c r="C6" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D6" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="E6" s="46" t="s">
+        <v>95</v>
+      </c>
+      <c r="F6" s="42" t="s">
+        <v>75</v>
+      </c>
+      <c r="G6" s="44" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B6" s="41" t="s">
+      <c r="H6" s="48" t="s">
+        <v>89</v>
+      </c>
+      <c r="I6" s="49"/>
+      <c r="J6" s="48" t="s">
+        <v>89</v>
+      </c>
+      <c r="K6" s="49"/>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B7" s="47"/>
+      <c r="C7" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D7" s="41" t="s">
         <v>87</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="D6" s="56" t="s">
-        <v>93</v>
-      </c>
-      <c r="E6" s="58" t="s">
-        <v>101</v>
-      </c>
-      <c r="F6" s="53" t="s">
-        <v>81</v>
-      </c>
-      <c r="G6" s="55" t="s">
-        <v>110</v>
-      </c>
-      <c r="H6" s="45" t="s">
+      <c r="E7" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="I6" s="46"/>
-      <c r="J6" s="45" t="s">
+      <c r="F7" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="G7" s="46" t="s">
+        <v>104</v>
+      </c>
+      <c r="H7" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="I7" s="46" t="s">
+        <v>97</v>
+      </c>
+      <c r="J7" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="K7" s="46" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.4">
+      <c r="B8" s="47"/>
+      <c r="C8" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D8" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="E8" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="K6" s="46"/>
-    </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B7" s="41"/>
-      <c r="C7" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="D7" s="56" t="s">
-        <v>93</v>
-      </c>
-      <c r="E7" s="58" t="s">
-        <v>101</v>
-      </c>
-      <c r="F7" s="56" t="s">
-        <v>93</v>
-      </c>
-      <c r="G7" s="58" t="s">
-        <v>110</v>
-      </c>
-      <c r="H7" s="56" t="s">
-        <v>93</v>
-      </c>
-      <c r="I7" s="58" t="s">
-        <v>103</v>
-      </c>
-      <c r="J7" s="56" t="s">
-        <v>93</v>
-      </c>
-      <c r="K7" s="58" t="s">
+      <c r="F8" s="42" t="s">
+        <v>75</v>
+      </c>
+      <c r="G8" s="44" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B8" s="41"/>
-      <c r="C8" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D8" s="56" t="s">
-        <v>93</v>
-      </c>
-      <c r="E8" s="58" t="s">
-        <v>101</v>
-      </c>
-      <c r="F8" s="53" t="s">
-        <v>81</v>
-      </c>
-      <c r="G8" s="55" t="s">
-        <v>110</v>
-      </c>
-      <c r="H8" s="56" t="s">
-        <v>93</v>
-      </c>
-      <c r="I8" s="58" t="s">
-        <v>103</v>
-      </c>
-      <c r="J8" s="56" t="s">
-        <v>93</v>
-      </c>
-      <c r="K8" s="58" t="s">
-        <v>104</v>
+      <c r="H8" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="I8" s="46" t="s">
+        <v>97</v>
+      </c>
+      <c r="J8" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="K8" s="46" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B13" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B14" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B15" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B18" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B19" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C19" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B20" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -3928,4 +4246,468 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F22D188F-8BB9-403B-A1C1-A54DF31F4D4C}">
+  <dimension ref="A1:F54"/>
+  <sheetFormatPr defaultColWidth="3.125" defaultRowHeight="15.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="16384" width="3.125" style="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="21" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="60" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="16.5" thickTop="1" x14ac:dyDescent="0.4"/>
+    <row r="3" spans="1:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B3" s="61" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="C4" s="7" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B6" s="61" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="18.75" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C8" s="8" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F9" s="7" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F10" s="7" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="18.75" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C12" s="8" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="18.75" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="D14" s="8" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F15" s="7" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="F16" s="7" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="18" spans="4:6" ht="18.75" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="D18" s="8" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="20" spans="4:6" ht="18.75" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="E20" s="8" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="21" spans="4:6" x14ac:dyDescent="0.4">
+      <c r="F21" s="7" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="22" spans="4:6" x14ac:dyDescent="0.4">
+      <c r="F22" s="7" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="24" spans="4:6" ht="18.75" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="E24" s="8" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="25" spans="4:6" x14ac:dyDescent="0.4">
+      <c r="F25" s="7" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="26" spans="4:6" x14ac:dyDescent="0.4">
+      <c r="F26" s="7" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="28" spans="4:6" ht="18.75" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="E28" s="8" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="29" spans="4:6" x14ac:dyDescent="0.4">
+      <c r="F29" s="7" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="30" spans="4:6" x14ac:dyDescent="0.4">
+      <c r="F30" s="7" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="32" spans="4:6" ht="18.75" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="E32" s="8" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="F33" s="7" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="F34" s="7" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="36" spans="2:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B36" s="61" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="38" spans="2:6" ht="18.75" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C38" s="8" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="39" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="D39" s="7" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="40" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="D40" s="7" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="42" spans="2:6" ht="18.75" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C42" s="8" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="43" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="D43" s="7" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="44" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="D44" s="7" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="46" spans="2:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B46" s="61" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="48" spans="2:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C48" s="61" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="49" spans="3:4" x14ac:dyDescent="0.4">
+      <c r="D49" s="7" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="50" spans="3:4" x14ac:dyDescent="0.4">
+      <c r="D50" s="7" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="52" spans="3:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C52" s="61" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="53" spans="3:4" x14ac:dyDescent="0.4">
+      <c r="D53" s="7" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="54" spans="3:4" x14ac:dyDescent="0.4">
+      <c r="D54" s="7" t="s">
+        <v>134</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E270B436-90A0-4E36-9AF0-C199521AEFF8}">
+  <dimension ref="A1:AD12"/>
+  <sheetFormatPr defaultColWidth="3.125" defaultRowHeight="15.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="16384" width="3.125" style="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:30" ht="21" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="60" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30" ht="16.5" thickTop="1" x14ac:dyDescent="0.4"/>
+    <row r="3" spans="1:30" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="B3" s="61" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="4" spans="1:30" x14ac:dyDescent="0.4">
+      <c r="C4" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30" x14ac:dyDescent="0.4">
+      <c r="D6" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="K6" s="19"/>
+      <c r="L6" s="19"/>
+      <c r="M6" s="19"/>
+      <c r="N6" s="20"/>
+      <c r="O6" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="P6" s="19"/>
+      <c r="Q6" s="19"/>
+      <c r="R6" s="19"/>
+      <c r="S6" s="19"/>
+      <c r="T6" s="19"/>
+      <c r="U6" s="19"/>
+      <c r="V6" s="20"/>
+      <c r="W6" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="X6" s="19"/>
+      <c r="Y6" s="19"/>
+      <c r="Z6" s="19"/>
+      <c r="AA6" s="19"/>
+      <c r="AB6" s="19"/>
+      <c r="AC6" s="19"/>
+      <c r="AD6" s="20"/>
+    </row>
+    <row r="7" spans="1:30" x14ac:dyDescent="0.4">
+      <c r="D7" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="K7" s="19"/>
+      <c r="L7" s="19"/>
+      <c r="M7" s="19"/>
+      <c r="N7" s="20"/>
+      <c r="O7" s="18"/>
+      <c r="P7" s="19"/>
+      <c r="Q7" s="19"/>
+      <c r="R7" s="19"/>
+      <c r="S7" s="19"/>
+      <c r="T7" s="19"/>
+      <c r="U7" s="19"/>
+      <c r="V7" s="20"/>
+      <c r="W7" s="18"/>
+      <c r="X7" s="19"/>
+      <c r="Y7" s="19"/>
+      <c r="Z7" s="19"/>
+      <c r="AA7" s="19"/>
+      <c r="AB7" s="19"/>
+      <c r="AC7" s="19"/>
+      <c r="AD7" s="20"/>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.4">
+      <c r="D8" s="15"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="K8" s="19"/>
+      <c r="L8" s="19"/>
+      <c r="M8" s="19"/>
+      <c r="N8" s="20"/>
+      <c r="O8" s="18"/>
+      <c r="P8" s="19"/>
+      <c r="Q8" s="19"/>
+      <c r="R8" s="19"/>
+      <c r="S8" s="19"/>
+      <c r="T8" s="19"/>
+      <c r="U8" s="19"/>
+      <c r="V8" s="20"/>
+      <c r="W8" s="18"/>
+      <c r="X8" s="19"/>
+      <c r="Y8" s="19"/>
+      <c r="Z8" s="19"/>
+      <c r="AA8" s="19"/>
+      <c r="AB8" s="19"/>
+      <c r="AC8" s="19"/>
+      <c r="AD8" s="20"/>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.4">
+      <c r="D9" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="K9" s="19"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="18"/>
+      <c r="P9" s="19"/>
+      <c r="Q9" s="19"/>
+      <c r="R9" s="19"/>
+      <c r="S9" s="19"/>
+      <c r="T9" s="19"/>
+      <c r="U9" s="19"/>
+      <c r="V9" s="20"/>
+      <c r="W9" s="18"/>
+      <c r="X9" s="19"/>
+      <c r="Y9" s="19"/>
+      <c r="Z9" s="19"/>
+      <c r="AA9" s="19"/>
+      <c r="AB9" s="19"/>
+      <c r="AC9" s="19"/>
+      <c r="AD9" s="20"/>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.4">
+      <c r="D10" s="15"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="17"/>
+      <c r="J10" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="K10" s="19"/>
+      <c r="L10" s="19"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="20"/>
+      <c r="O10" s="18"/>
+      <c r="P10" s="19"/>
+      <c r="Q10" s="19"/>
+      <c r="R10" s="19"/>
+      <c r="S10" s="19"/>
+      <c r="T10" s="19"/>
+      <c r="U10" s="19"/>
+      <c r="V10" s="20"/>
+      <c r="W10" s="18"/>
+      <c r="X10" s="19"/>
+      <c r="Y10" s="19"/>
+      <c r="Z10" s="19"/>
+      <c r="AA10" s="19"/>
+      <c r="AB10" s="19"/>
+      <c r="AC10" s="19"/>
+      <c r="AD10" s="20"/>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.4">
+      <c r="D11" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="12"/>
+      <c r="J11" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="20"/>
+      <c r="O11" s="18"/>
+      <c r="P11" s="19"/>
+      <c r="Q11" s="19"/>
+      <c r="R11" s="19"/>
+      <c r="S11" s="19"/>
+      <c r="T11" s="19"/>
+      <c r="U11" s="19"/>
+      <c r="V11" s="20"/>
+      <c r="W11" s="18"/>
+      <c r="X11" s="19"/>
+      <c r="Y11" s="19"/>
+      <c r="Z11" s="19"/>
+      <c r="AA11" s="19"/>
+      <c r="AB11" s="19"/>
+      <c r="AC11" s="19"/>
+      <c r="AD11" s="20"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.4">
+      <c r="D12" s="15"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="K12" s="19"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="20"/>
+      <c r="O12" s="18"/>
+      <c r="P12" s="19"/>
+      <c r="Q12" s="19"/>
+      <c r="R12" s="19"/>
+      <c r="S12" s="19"/>
+      <c r="T12" s="19"/>
+      <c r="U12" s="19"/>
+      <c r="V12" s="20"/>
+      <c r="W12" s="18"/>
+      <c r="X12" s="19"/>
+      <c r="Y12" s="19"/>
+      <c r="Z12" s="19"/>
+      <c r="AA12" s="19"/>
+      <c r="AB12" s="19"/>
+      <c r="AC12" s="19"/>
+      <c r="AD12" s="20"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/調査内容/アウトプット.xlsx
+++ b/調査内容/アウトプット.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\aaa\elkstack\調査内容\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C811044-B071-4A6E-8B21-6119AB383405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E52D7EAA-7568-44C2-96CD-C12621354522}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{FE37317B-BE23-49EA-9156-A5F997289FA1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{FE37317B-BE23-49EA-9156-A5F997289FA1}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="135">
   <si>
     <t>徐々に上昇、減少する値が一定値を超えたら</t>
     <rPh sb="0" eb="2">
@@ -1086,16 +1086,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>1. スケジュールとループバック時間の設定</t>
-    <rPh sb="16" eb="18">
-      <t>ジカン</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>セッテイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>2. グループ化</t>
     <rPh sb="7" eb="8">
       <t>カ</t>
@@ -1103,19 +1093,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>3. 状態変化通知</t>
-    <rPh sb="3" eb="5">
-      <t>ジョウタイ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ヘンカ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ツウチ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>期間集計した結果で検知</t>
     <rPh sb="0" eb="2">
       <t>キカン</t>
@@ -1132,22 +1109,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>中央値</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>平均値</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>最高値</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>最低値</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>（設定方法）</t>
     <rPh sb="1" eb="3">
       <t>セッテイ</t>
@@ -1165,47 +1126,7 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>継続通知</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>状態変化通知</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>4. アラート重複排除・抑制</t>
-    <rPh sb="7" eb="9">
-      <t>ジュウフク</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ハイジョ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>ヨクセイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>1. アラート制御方法</t>
-    <rPh sb="7" eb="9">
-      <t>セイギョ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>ホウホウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>複数件で判定</t>
-    <rPh sb="0" eb="2">
-      <t>フクスウ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>ケン</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ハンテイ</t>
-    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1229,6 +1150,27 @@
     <rPh sb="5" eb="7">
       <t>ジョウケン</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1. アラート</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>（設定手順）</t>
+    <rPh sb="1" eb="3">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>テジュン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FROM sensor-data-*
+ | WHERE device_id.keyword == "pump-01" AND vibration &gt;= 6.2
+ | EVAL vibration = ROUND(vibration, 2)
+ | KEEP @timestamp, device_id, vibration</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1551,7 +1493,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1693,50 +1635,47 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="4" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="2" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="4" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="2" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2564,38 +2503,38 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:15" x14ac:dyDescent="0.4">
-      <c r="D3" s="54" t="s">
+      <c r="D3" s="50" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="54"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="54"/>
-      <c r="I3" s="54"/>
-      <c r="J3" s="54"/>
-      <c r="K3" s="54"/>
-      <c r="L3" s="54"/>
-      <c r="M3" s="54"/>
-      <c r="N3" s="54"/>
-      <c r="O3" s="54"/>
+      <c r="E3" s="50"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="50"/>
+      <c r="K3" s="50"/>
+      <c r="L3" s="50"/>
+      <c r="M3" s="50"/>
+      <c r="N3" s="50"/>
+      <c r="O3" s="50"/>
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.4">
-      <c r="D4" s="47" t="s">
+      <c r="D4" s="49" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="49"/>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.4">
       <c r="D5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="47" t="s">
+      <c r="E5" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="47"/>
-      <c r="G5" s="47"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.4">
       <c r="D6" s="3" t="s">
@@ -2650,11 +2589,11 @@
       <c r="C9" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="59" t="s">
+      <c r="D9" s="4" t="s">
         <v>106</v>
       </c>
       <c r="E9" s="4"/>
-      <c r="F9" s="59" t="s">
+      <c r="F9" s="4" t="s">
         <v>107</v>
       </c>
       <c r="G9" s="4"/>
@@ -2663,11 +2602,11 @@
       <c r="C10" t="s">
         <v>90</v>
       </c>
-      <c r="D10" s="59" t="s">
+      <c r="D10" s="4" t="s">
         <v>105</v>
       </c>
       <c r="E10" s="4"/>
-      <c r="F10" s="59" t="s">
+      <c r="F10" s="4" t="s">
         <v>108</v>
       </c>
       <c r="G10" s="4"/>
@@ -2679,11 +2618,11 @@
       <c r="C11" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="59" t="s">
+      <c r="D11" s="4" t="s">
         <v>25</v>
       </c>
       <c r="E11" s="4"/>
-      <c r="F11" s="59" t="s">
+      <c r="F11" s="4" t="s">
         <v>109</v>
       </c>
       <c r="G11" s="4"/>
@@ -2692,11 +2631,11 @@
       <c r="C12" t="s">
         <v>90</v>
       </c>
-      <c r="D12" s="59" t="s">
+      <c r="D12" s="4" t="s">
         <v>105</v>
       </c>
       <c r="E12" s="4"/>
-      <c r="F12" s="59" t="s">
+      <c r="F12" s="4" t="s">
         <v>108</v>
       </c>
       <c r="G12" s="4"/>
@@ -2725,67 +2664,70 @@
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
     </row>
-    <row r="17" spans="4:7" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.4">
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
     </row>
-    <row r="18" spans="4:7" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.4">
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
       <c r="G18" s="4"/>
     </row>
-    <row r="19" spans="4:7" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:7" ht="168.75" x14ac:dyDescent="0.4">
+      <c r="B19" s="1" t="s">
+        <v>134</v>
+      </c>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
     </row>
-    <row r="20" spans="4:7" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.4">
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
       <c r="G20" s="4"/>
     </row>
-    <row r="21" spans="4:7" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.4">
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
     </row>
-    <row r="22" spans="4:7" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.4">
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
     </row>
-    <row r="23" spans="4:7" x14ac:dyDescent="0.4">
+    <row r="23" spans="2:7" x14ac:dyDescent="0.4">
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
     </row>
-    <row r="24" spans="4:7" x14ac:dyDescent="0.4">
+    <row r="24" spans="2:7" x14ac:dyDescent="0.4">
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
       <c r="G24" s="4"/>
     </row>
-    <row r="25" spans="4:7" x14ac:dyDescent="0.4">
+    <row r="25" spans="2:7" x14ac:dyDescent="0.4">
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
       <c r="G25" s="4"/>
     </row>
-    <row r="26" spans="4:7" x14ac:dyDescent="0.4">
+    <row r="26" spans="2:7" x14ac:dyDescent="0.4">
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
     </row>
-    <row r="27" spans="4:7" x14ac:dyDescent="0.4">
+    <row r="27" spans="2:7" x14ac:dyDescent="0.4">
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
@@ -3253,24 +3195,24 @@
       <c r="AC22" s="19"/>
       <c r="AD22" s="19"/>
       <c r="AE22" s="20"/>
-      <c r="AF22" s="56" t="s">
+      <c r="AF22" s="52" t="s">
         <v>75</v>
       </c>
-      <c r="AG22" s="57"/>
-      <c r="AH22" s="57"/>
-      <c r="AI22" s="58"/>
-      <c r="AJ22" s="55" t="s">
+      <c r="AG22" s="53"/>
+      <c r="AH22" s="53"/>
+      <c r="AI22" s="54"/>
+      <c r="AJ22" s="51" t="s">
         <v>75</v>
       </c>
-      <c r="AK22" s="55"/>
-      <c r="AL22" s="55"/>
-      <c r="AM22" s="55"/>
-      <c r="AN22" s="55" t="s">
+      <c r="AK22" s="51"/>
+      <c r="AL22" s="51"/>
+      <c r="AM22" s="51"/>
+      <c r="AN22" s="51" t="s">
         <v>75</v>
       </c>
-      <c r="AO22" s="55"/>
-      <c r="AP22" s="55"/>
-      <c r="AQ22" s="55"/>
+      <c r="AO22" s="51"/>
+      <c r="AP22" s="51"/>
+      <c r="AQ22" s="51"/>
     </row>
     <row r="23" spans="3:43" x14ac:dyDescent="0.4">
       <c r="C23" s="18" t="s">
@@ -3306,24 +3248,24 @@
       <c r="AC23" s="19"/>
       <c r="AD23" s="19"/>
       <c r="AE23" s="20"/>
-      <c r="AF23" s="56" t="s">
+      <c r="AF23" s="52" t="s">
         <v>76</v>
       </c>
-      <c r="AG23" s="57"/>
-      <c r="AH23" s="57"/>
-      <c r="AI23" s="58"/>
-      <c r="AJ23" s="55" t="s">
+      <c r="AG23" s="53"/>
+      <c r="AH23" s="53"/>
+      <c r="AI23" s="54"/>
+      <c r="AJ23" s="51" t="s">
         <v>75</v>
       </c>
-      <c r="AK23" s="55"/>
-      <c r="AL23" s="55"/>
-      <c r="AM23" s="55"/>
-      <c r="AN23" s="55" t="s">
+      <c r="AK23" s="51"/>
+      <c r="AL23" s="51"/>
+      <c r="AM23" s="51"/>
+      <c r="AN23" s="51" t="s">
         <v>75</v>
       </c>
-      <c r="AO23" s="55"/>
-      <c r="AP23" s="55"/>
-      <c r="AQ23" s="55"/>
+      <c r="AO23" s="51"/>
+      <c r="AP23" s="51"/>
+      <c r="AQ23" s="51"/>
     </row>
     <row r="24" spans="3:43" x14ac:dyDescent="0.4">
       <c r="C24" s="18" t="s">
@@ -3359,24 +3301,24 @@
       <c r="AC24" s="19"/>
       <c r="AD24" s="19"/>
       <c r="AE24" s="20"/>
-      <c r="AF24" s="56" t="s">
+      <c r="AF24" s="52" t="s">
         <v>76</v>
       </c>
-      <c r="AG24" s="57"/>
-      <c r="AH24" s="57"/>
-      <c r="AI24" s="58"/>
-      <c r="AJ24" s="55" t="s">
+      <c r="AG24" s="53"/>
+      <c r="AH24" s="53"/>
+      <c r="AI24" s="54"/>
+      <c r="AJ24" s="51" t="s">
         <v>75</v>
       </c>
-      <c r="AK24" s="55"/>
-      <c r="AL24" s="55"/>
-      <c r="AM24" s="55"/>
-      <c r="AN24" s="55" t="s">
+      <c r="AK24" s="51"/>
+      <c r="AL24" s="51"/>
+      <c r="AM24" s="51"/>
+      <c r="AN24" s="51" t="s">
         <v>75</v>
       </c>
-      <c r="AO24" s="55"/>
-      <c r="AP24" s="55"/>
-      <c r="AQ24" s="55"/>
+      <c r="AO24" s="51"/>
+      <c r="AP24" s="51"/>
+      <c r="AQ24" s="51"/>
     </row>
     <row r="25" spans="3:43" x14ac:dyDescent="0.4">
       <c r="C25" s="18" t="s">
@@ -3412,24 +3354,24 @@
       <c r="AC25" s="19"/>
       <c r="AD25" s="19"/>
       <c r="AE25" s="20"/>
-      <c r="AF25" s="56" t="s">
+      <c r="AF25" s="52" t="s">
         <v>76</v>
       </c>
-      <c r="AG25" s="57"/>
-      <c r="AH25" s="57"/>
-      <c r="AI25" s="58"/>
-      <c r="AJ25" s="55" t="s">
+      <c r="AG25" s="53"/>
+      <c r="AH25" s="53"/>
+      <c r="AI25" s="54"/>
+      <c r="AJ25" s="51" t="s">
         <v>75</v>
       </c>
-      <c r="AK25" s="55"/>
-      <c r="AL25" s="55"/>
-      <c r="AM25" s="55"/>
-      <c r="AN25" s="55" t="s">
+      <c r="AK25" s="51"/>
+      <c r="AL25" s="51"/>
+      <c r="AM25" s="51"/>
+      <c r="AN25" s="51" t="s">
         <v>75</v>
       </c>
-      <c r="AO25" s="55"/>
-      <c r="AP25" s="55"/>
-      <c r="AQ25" s="55"/>
+      <c r="AO25" s="51"/>
+      <c r="AP25" s="51"/>
+      <c r="AQ25" s="51"/>
     </row>
     <row r="26" spans="3:43" x14ac:dyDescent="0.4">
       <c r="C26" s="18" t="s">
@@ -3465,24 +3407,24 @@
       <c r="AC26" s="19"/>
       <c r="AD26" s="19"/>
       <c r="AE26" s="20"/>
-      <c r="AF26" s="55" t="s">
+      <c r="AF26" s="51" t="s">
         <v>75</v>
       </c>
-      <c r="AG26" s="55"/>
-      <c r="AH26" s="55"/>
-      <c r="AI26" s="55"/>
-      <c r="AJ26" s="55" t="s">
+      <c r="AG26" s="51"/>
+      <c r="AH26" s="51"/>
+      <c r="AI26" s="51"/>
+      <c r="AJ26" s="51" t="s">
         <v>75</v>
       </c>
-      <c r="AK26" s="55"/>
-      <c r="AL26" s="55"/>
-      <c r="AM26" s="55"/>
-      <c r="AN26" s="55" t="s">
+      <c r="AK26" s="51"/>
+      <c r="AL26" s="51"/>
+      <c r="AM26" s="51"/>
+      <c r="AN26" s="51" t="s">
         <v>75</v>
       </c>
-      <c r="AO26" s="55"/>
-      <c r="AP26" s="55"/>
-      <c r="AQ26" s="55"/>
+      <c r="AO26" s="51"/>
+      <c r="AP26" s="51"/>
+      <c r="AQ26" s="51"/>
     </row>
     <row r="27" spans="3:43" x14ac:dyDescent="0.4">
       <c r="C27" s="18" t="s">
@@ -3518,24 +3460,24 @@
       <c r="AC27" s="19"/>
       <c r="AD27" s="19"/>
       <c r="AE27" s="20"/>
-      <c r="AF27" s="55" t="s">
+      <c r="AF27" s="51" t="s">
         <v>75</v>
       </c>
-      <c r="AG27" s="55"/>
-      <c r="AH27" s="55"/>
-      <c r="AI27" s="55"/>
-      <c r="AJ27" s="55" t="s">
+      <c r="AG27" s="51"/>
+      <c r="AH27" s="51"/>
+      <c r="AI27" s="51"/>
+      <c r="AJ27" s="51" t="s">
         <v>75</v>
       </c>
-      <c r="AK27" s="55"/>
-      <c r="AL27" s="55"/>
-      <c r="AM27" s="55"/>
-      <c r="AN27" s="55" t="s">
+      <c r="AK27" s="51"/>
+      <c r="AL27" s="51"/>
+      <c r="AM27" s="51"/>
+      <c r="AN27" s="51" t="s">
         <v>75</v>
       </c>
-      <c r="AO27" s="55"/>
-      <c r="AP27" s="55"/>
-      <c r="AQ27" s="55"/>
+      <c r="AO27" s="51"/>
+      <c r="AP27" s="51"/>
+      <c r="AQ27" s="51"/>
     </row>
     <row r="28" spans="3:43" x14ac:dyDescent="0.4">
       <c r="C28" s="18" t="s">
@@ -3571,24 +3513,24 @@
       <c r="AC28" s="19"/>
       <c r="AD28" s="19"/>
       <c r="AE28" s="20"/>
-      <c r="AF28" s="55" t="s">
+      <c r="AF28" s="51" t="s">
         <v>75</v>
       </c>
-      <c r="AG28" s="55"/>
-      <c r="AH28" s="55"/>
-      <c r="AI28" s="55"/>
-      <c r="AJ28" s="55" t="s">
+      <c r="AG28" s="51"/>
+      <c r="AH28" s="51"/>
+      <c r="AI28" s="51"/>
+      <c r="AJ28" s="51" t="s">
         <v>75</v>
       </c>
-      <c r="AK28" s="55"/>
-      <c r="AL28" s="55"/>
-      <c r="AM28" s="55"/>
-      <c r="AN28" s="55" t="s">
+      <c r="AK28" s="51"/>
+      <c r="AL28" s="51"/>
+      <c r="AM28" s="51"/>
+      <c r="AN28" s="51" t="s">
         <v>75</v>
       </c>
-      <c r="AO28" s="55"/>
-      <c r="AP28" s="55"/>
-      <c r="AQ28" s="55"/>
+      <c r="AO28" s="51"/>
+      <c r="AP28" s="51"/>
+      <c r="AQ28" s="51"/>
     </row>
     <row r="49" spans="3:3" x14ac:dyDescent="0.4">
       <c r="C49" s="7" t="s">
@@ -3763,13 +3705,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="AN28:AQ28"/>
-    <mergeCell ref="AN22:AQ22"/>
-    <mergeCell ref="AN23:AQ23"/>
-    <mergeCell ref="AN24:AQ24"/>
-    <mergeCell ref="AN25:AQ25"/>
-    <mergeCell ref="AN26:AQ26"/>
-    <mergeCell ref="AN27:AQ27"/>
     <mergeCell ref="AJ28:AM28"/>
     <mergeCell ref="AJ22:AM22"/>
     <mergeCell ref="AF22:AI22"/>
@@ -3784,6 +3719,13 @@
     <mergeCell ref="AJ25:AM25"/>
     <mergeCell ref="AJ26:AM26"/>
     <mergeCell ref="AJ27:AM27"/>
+    <mergeCell ref="AN28:AQ28"/>
+    <mergeCell ref="AN22:AQ22"/>
+    <mergeCell ref="AN23:AQ23"/>
+    <mergeCell ref="AN24:AQ24"/>
+    <mergeCell ref="AN25:AQ25"/>
+    <mergeCell ref="AN26:AQ26"/>
+    <mergeCell ref="AN27:AQ27"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <hyperlinks>
@@ -3811,43 +3753,43 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="50" t="s">
+      <c r="B2" s="49"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="55" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="51" t="s">
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="56" t="s">
         <v>90</v>
       </c>
-      <c r="I2" s="51"/>
-      <c r="J2" s="51"/>
-      <c r="K2" s="51"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="50" t="s">
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="55" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="50"/>
-      <c r="F3" s="50" t="s">
+      <c r="E3" s="55"/>
+      <c r="F3" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="50"/>
-      <c r="H3" s="51" t="s">
+      <c r="G3" s="55"/>
+      <c r="H3" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="51"/>
-      <c r="J3" s="52" t="s">
+      <c r="I3" s="56"/>
+      <c r="J3" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="53"/>
+      <c r="K3" s="60"/>
     </row>
     <row r="4" spans="2:11" ht="37.5" x14ac:dyDescent="0.4">
-      <c r="B4" s="47" t="s">
+      <c r="B4" s="49" t="s">
         <v>80</v>
       </c>
       <c r="C4" s="4" t="s">
@@ -3879,7 +3821,7 @@
       </c>
     </row>
     <row r="5" spans="2:11" ht="56.25" x14ac:dyDescent="0.4">
-      <c r="B5" s="47"/>
+      <c r="B5" s="49"/>
       <c r="C5" s="4" t="s">
         <v>86</v>
       </c>
@@ -3907,7 +3849,7 @@
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B6" s="47" t="s">
+      <c r="B6" s="49" t="s">
         <v>81</v>
       </c>
       <c r="C6" s="4" t="s">
@@ -3921,17 +3863,17 @@
         <v>75</v>
       </c>
       <c r="G6" s="38"/>
-      <c r="H6" s="48" t="s">
+      <c r="H6" s="57" t="s">
         <v>89</v>
       </c>
-      <c r="I6" s="49"/>
-      <c r="J6" s="48" t="s">
+      <c r="I6" s="58"/>
+      <c r="J6" s="57" t="s">
         <v>89</v>
       </c>
-      <c r="K6" s="49"/>
+      <c r="K6" s="58"/>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B7" s="47"/>
+      <c r="B7" s="49"/>
       <c r="C7" s="4" t="s">
         <v>83</v>
       </c>
@@ -3953,7 +3895,7 @@
       <c r="K7" s="38"/>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B8" s="47"/>
+      <c r="B8" s="49"/>
       <c r="C8" s="4" t="s">
         <v>84</v>
       </c>
@@ -4011,43 +3953,43 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="50" t="s">
+      <c r="B2" s="49"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="55" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="51" t="s">
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="56" t="s">
         <v>90</v>
       </c>
-      <c r="I2" s="51"/>
-      <c r="J2" s="51"/>
-      <c r="K2" s="51"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="50" t="s">
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="55" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="50"/>
-      <c r="F3" s="50" t="s">
+      <c r="E3" s="55"/>
+      <c r="F3" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="50"/>
-      <c r="H3" s="51" t="s">
+      <c r="G3" s="55"/>
+      <c r="H3" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="51"/>
-      <c r="J3" s="52" t="s">
+      <c r="I3" s="56"/>
+      <c r="J3" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="K3" s="53"/>
+      <c r="K3" s="60"/>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B4" s="47" t="s">
+      <c r="B4" s="49" t="s">
         <v>80</v>
       </c>
       <c r="C4" s="4" t="s">
@@ -4079,7 +4021,7 @@
       </c>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B5" s="47"/>
+      <c r="B5" s="49"/>
       <c r="C5" s="4" t="s">
         <v>86</v>
       </c>
@@ -4109,7 +4051,7 @@
       </c>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B6" s="47" t="s">
+      <c r="B6" s="49" t="s">
         <v>81</v>
       </c>
       <c r="C6" s="4" t="s">
@@ -4127,17 +4069,17 @@
       <c r="G6" s="44" t="s">
         <v>104</v>
       </c>
-      <c r="H6" s="48" t="s">
+      <c r="H6" s="57" t="s">
         <v>89</v>
       </c>
-      <c r="I6" s="49"/>
-      <c r="J6" s="48" t="s">
+      <c r="I6" s="58"/>
+      <c r="J6" s="57" t="s">
         <v>89</v>
       </c>
-      <c r="K6" s="49"/>
+      <c r="K6" s="58"/>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B7" s="47"/>
+      <c r="B7" s="49"/>
       <c r="C7" s="4" t="s">
         <v>83</v>
       </c>
@@ -4167,7 +4109,7 @@
       </c>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.4">
-      <c r="B8" s="47"/>
+      <c r="B8" s="49"/>
       <c r="C8" s="4" t="s">
         <v>84</v>
       </c>
@@ -4250,20 +4192,20 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F22D188F-8BB9-403B-A1C1-A54DF31F4D4C}">
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr defaultColWidth="3.125" defaultRowHeight="15.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="16384" width="3.125" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="60" t="s">
-        <v>138</v>
+      <c r="A1" s="47" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="16.5" thickTop="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="1:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="61" t="s">
+      <c r="B3" s="48" t="s">
         <v>123</v>
       </c>
     </row>
@@ -4273,178 +4215,78 @@
       </c>
     </row>
     <row r="6" spans="1:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B6" s="61" t="s">
-        <v>141</v>
+      <c r="B6" s="48" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="18.75" thickBot="1" x14ac:dyDescent="0.45">
       <c r="C8" s="8" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.4">
       <c r="F9" s="7" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.4">
       <c r="F10" s="7" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="18.75" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="C12" s="8" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="18.75" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="D14" s="8" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="18.75" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="D16" s="8" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="20" spans="3:5" x14ac:dyDescent="0.4">
+      <c r="E20" s="7" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="29" spans="3:5" ht="18.75" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C29" s="8" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="F15" s="7" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="F16" s="7" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="18" spans="4:6" ht="18.75" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="D18" s="8" t="s">
+    <row r="30" spans="3:5" x14ac:dyDescent="0.4">
+      <c r="D30" s="7" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="31" spans="3:5" x14ac:dyDescent="0.4">
+      <c r="D31" s="7" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="20" spans="4:6" ht="18.75" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="E20" s="8" t="s">
+    <row r="34" spans="3:4" ht="18.75" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C34" s="8" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="21" spans="4:6" x14ac:dyDescent="0.4">
-      <c r="F21" s="7" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="22" spans="4:6" x14ac:dyDescent="0.4">
-      <c r="F22" s="7" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="24" spans="4:6" ht="18.75" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="E24" s="8" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="25" spans="4:6" x14ac:dyDescent="0.4">
-      <c r="F25" s="7" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="26" spans="4:6" x14ac:dyDescent="0.4">
-      <c r="F26" s="7" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="28" spans="4:6" ht="18.75" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="E28" s="8" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="29" spans="4:6" x14ac:dyDescent="0.4">
-      <c r="F29" s="7" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="30" spans="4:6" x14ac:dyDescent="0.4">
-      <c r="F30" s="7" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="32" spans="4:6" ht="18.75" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="E32" s="8" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="F33" s="7" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="F34" s="7" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="36" spans="2:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B36" s="61" t="s">
+    <row r="35" spans="3:4" x14ac:dyDescent="0.4">
+      <c r="D35" s="7" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="38" spans="2:6" ht="18.75" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="C38" s="8" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="36" spans="3:4" x14ac:dyDescent="0.4">
+      <c r="D36" s="7" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="38" spans="3:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C38" s="48" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="39" spans="3:4" x14ac:dyDescent="0.4">
       <c r="D39" s="7" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.4">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="40" spans="3:4" x14ac:dyDescent="0.4">
       <c r="D40" s="7" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="42" spans="2:6" ht="18.75" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="C42" s="8" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="D43" s="7" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="D44" s="7" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="46" spans="2:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B46" s="61" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="48" spans="2:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="C48" s="61" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="49" spans="3:4" x14ac:dyDescent="0.4">
-      <c r="D49" s="7" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="50" spans="3:4" x14ac:dyDescent="0.4">
-      <c r="D50" s="7" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="52" spans="3:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="C52" s="61" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="53" spans="3:4" x14ac:dyDescent="0.4">
-      <c r="D53" s="7" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="54" spans="3:4" x14ac:dyDescent="0.4">
-      <c r="D54" s="7" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -4462,13 +4304,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" ht="21" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="47" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:30" ht="16.5" thickTop="1" x14ac:dyDescent="0.4"/>
     <row r="3" spans="1:30" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="61" t="s">
+      <c r="B3" s="48" t="s">
         <v>121</v>
       </c>
     </row>
